--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393636</v>
+        <v>122393599</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650878</v>
+        <v>650684</v>
       </c>
       <c r="R2" t="n">
-        <v>6672405</v>
+        <v>6672094</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393617</v>
+        <v>122393624</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>91404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650568</v>
+        <v>650798</v>
       </c>
       <c r="R3" t="n">
-        <v>6671929</v>
+        <v>6672223</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393611</v>
+        <v>122393589</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,37 +930,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650587</v>
+        <v>650540</v>
       </c>
       <c r="R4" t="n">
-        <v>6671963</v>
+        <v>6671903</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393640</v>
+        <v>122393598</v>
       </c>
       <c r="B5" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,42 +1050,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650907</v>
+        <v>650520</v>
       </c>
       <c r="R5" t="n">
-        <v>6672335</v>
+        <v>6671866</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393579</v>
+        <v>122393583</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,20 +1174,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1170,26 +1195,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650568</v>
+        <v>650841</v>
       </c>
       <c r="R6" t="n">
-        <v>6671816</v>
+        <v>6672286</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1221,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393583</v>
+        <v>122393579</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,20 +1298,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,29 +1319,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650841</v>
+        <v>650568</v>
       </c>
       <c r="R7" t="n">
-        <v>6672286</v>
+        <v>6671816</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1345,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393577</v>
+        <v>122393649</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,43 +1423,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650572</v>
+        <v>650513</v>
       </c>
       <c r="R8" t="n">
-        <v>6671983</v>
+        <v>6671875</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1466,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393647</v>
+        <v>122393628</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,29 +1535,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1547,10 +1575,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650531</v>
+        <v>650517</v>
       </c>
       <c r="R9" t="n">
-        <v>6671845</v>
+        <v>6671888</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1582,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393633</v>
+        <v>122393617</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>90789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,42 +1659,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650806</v>
+        <v>650568</v>
       </c>
       <c r="R10" t="n">
-        <v>6672399</v>
+        <v>6671929</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1698,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393637</v>
+        <v>122393622</v>
       </c>
       <c r="B11" t="n">
-        <v>100441</v>
+        <v>91182</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,42 +1774,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650982</v>
+        <v>650619</v>
       </c>
       <c r="R11" t="n">
-        <v>6672324</v>
+        <v>6671913</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1814,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1824,7 +1845,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1872,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393653</v>
+        <v>122393650</v>
       </c>
       <c r="B12" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,14 +1912,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650726</v>
+        <v>650527</v>
       </c>
       <c r="R12" t="n">
-        <v>6672208</v>
+        <v>6671884</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1930,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,7 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393670</v>
+        <v>122393623</v>
       </c>
       <c r="B13" t="n">
-        <v>90549</v>
+        <v>91404</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,21 +2004,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,14 +2027,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650673</v>
+        <v>650805</v>
       </c>
       <c r="R13" t="n">
-        <v>6672256</v>
+        <v>6672392</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2045,7 +2066,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2076,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393619</v>
+        <v>122390399</v>
       </c>
       <c r="B14" t="n">
-        <v>90779</v>
+        <v>57744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,30 +2115,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2125,13 +2151,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650561</v>
+        <v>650718</v>
       </c>
       <c r="R14" t="n">
-        <v>6671937</v>
+        <v>6672218</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2160,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,7 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,14 +2219,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393646</v>
+        <v>122393614</v>
       </c>
       <c r="B15" t="n">
-        <v>100441</v>
+        <v>90789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,31 +2239,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2241,10 +2270,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650560</v>
+        <v>650587</v>
       </c>
       <c r="R15" t="n">
-        <v>6671817</v>
+        <v>6671907</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2276,7 +2305,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2315,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2342,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393589</v>
+        <v>122393670</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>90559</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,50 +2354,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650540</v>
+        <v>650673</v>
       </c>
       <c r="R16" t="n">
-        <v>6671903</v>
+        <v>6672256</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2400,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393649</v>
+        <v>122393651</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,10 +2501,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650513</v>
+        <v>650521</v>
       </c>
       <c r="R17" t="n">
-        <v>6671875</v>
+        <v>6671872</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2516,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,10 +2573,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393632</v>
+        <v>122393653</v>
       </c>
       <c r="B18" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,14 +2613,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650791</v>
+        <v>650726</v>
       </c>
       <c r="R18" t="n">
-        <v>6672382</v>
+        <v>6672208</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2632,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2642,7 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393585</v>
+        <v>122393654</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>105290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,50 +2701,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650587</v>
+        <v>650496</v>
       </c>
       <c r="R19" t="n">
-        <v>6671916</v>
+        <v>6671860</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2756,7 +2772,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2782,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,10 +2809,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393628</v>
+        <v>122393642</v>
       </c>
       <c r="B20" t="n">
-        <v>98175</v>
+        <v>100451</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2805,50 +2821,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650517</v>
+        <v>650888</v>
       </c>
       <c r="R20" t="n">
-        <v>6671888</v>
+        <v>6672343</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2880,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2890,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393623</v>
+        <v>122393646</v>
       </c>
       <c r="B21" t="n">
-        <v>91394</v>
+        <v>100451</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,37 +2941,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650805</v>
+        <v>650560</v>
       </c>
       <c r="R21" t="n">
-        <v>6672392</v>
+        <v>6671817</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2995,7 +3004,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +3014,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,10 +3041,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393599</v>
+        <v>122393632</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,50 +3053,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650684</v>
+        <v>650791</v>
       </c>
       <c r="R22" t="n">
-        <v>6672094</v>
+        <v>6672382</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3119,7 +3120,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3130,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,10 +3157,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393651</v>
+        <v>122393578</v>
       </c>
       <c r="B23" t="n">
-        <v>100441</v>
+        <v>5193</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3172,27 +3173,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3200,10 +3206,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650521</v>
+        <v>650620</v>
       </c>
       <c r="R23" t="n">
-        <v>6671872</v>
+        <v>6671917</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3235,7 +3241,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3245,7 +3251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3272,10 +3278,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393634</v>
+        <v>122393610</v>
       </c>
       <c r="B24" t="n">
-        <v>100441</v>
+        <v>90754</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3288,38 +3294,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650818</v>
+        <v>650579</v>
       </c>
       <c r="R24" t="n">
-        <v>6672400</v>
+        <v>6671979</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3361,7 +3366,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3388,10 +3393,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393622</v>
+        <v>122393635</v>
       </c>
       <c r="B25" t="n">
-        <v>91172</v>
+        <v>100451</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3400,36 +3405,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650619</v>
+        <v>650861</v>
       </c>
       <c r="R25" t="n">
-        <v>6671913</v>
+        <v>6672364</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3461,7 +3472,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3471,7 +3482,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3498,10 +3509,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393598</v>
+        <v>122393637</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3510,50 +3521,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650520</v>
+        <v>650982</v>
       </c>
       <c r="R26" t="n">
-        <v>6671866</v>
+        <v>6672324</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3585,7 +3588,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3598,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,10 +3625,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393610</v>
+        <v>122393636</v>
       </c>
       <c r="B27" t="n">
-        <v>90744</v>
+        <v>100451</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3638,37 +3641,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650579</v>
+        <v>650878</v>
       </c>
       <c r="R27" t="n">
-        <v>6671979</v>
+        <v>6672405</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3700,7 +3704,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3710,7 +3714,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,10 +3741,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122390399</v>
+        <v>122393585</v>
       </c>
       <c r="B28" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3749,20 +3753,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3777,21 +3781,25 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650718</v>
+        <v>650587</v>
       </c>
       <c r="R28" t="n">
-        <v>6672218</v>
+        <v>6671916</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3820,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3830,7 +3838,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,18 +3861,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393604</v>
+        <v>122393634</v>
       </c>
       <c r="B29" t="n">
-        <v>57527</v>
+        <v>100451</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3873,49 +3877,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650559</v>
+        <v>650818</v>
       </c>
       <c r="R29" t="n">
-        <v>6671894</v>
+        <v>6672400</v>
       </c>
       <c r="S29" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3954,12 +3954,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3986,10 +3981,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393587</v>
+        <v>122393633</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3998,46 +3993,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650580</v>
+        <v>650806</v>
       </c>
       <c r="R30" t="n">
-        <v>6671917</v>
+        <v>6672399</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4069,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4079,7 +4070,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4106,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393654</v>
+        <v>122393611</v>
       </c>
       <c r="B31" t="n">
-        <v>105280</v>
+        <v>90789</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4118,46 +4109,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650496</v>
+        <v>650587</v>
       </c>
       <c r="R31" t="n">
-        <v>6671860</v>
+        <v>6671963</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4189,7 +4175,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4199,7 +4185,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4226,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393578</v>
+        <v>122393643</v>
       </c>
       <c r="B32" t="n">
-        <v>5193</v>
+        <v>100451</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4242,43 +4228,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650620</v>
+        <v>650851</v>
       </c>
       <c r="R32" t="n">
-        <v>6671917</v>
+        <v>6672282</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4310,7 +4291,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4320,7 +4301,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4347,10 +4328,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393635</v>
+        <v>122393647</v>
       </c>
       <c r="B33" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,14 +4368,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650861</v>
+        <v>650531</v>
       </c>
       <c r="R33" t="n">
-        <v>6672364</v>
+        <v>6671845</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4426,7 +4407,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4436,7 +4417,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4463,10 +4444,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393614</v>
+        <v>122393644</v>
       </c>
       <c r="B34" t="n">
-        <v>90779</v>
+        <v>100451</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4475,41 +4456,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650587</v>
+        <v>650753</v>
       </c>
       <c r="R34" t="n">
-        <v>6671907</v>
+        <v>6672196</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4541,7 +4523,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4551,7 +4533,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4560,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393624</v>
+        <v>122393640</v>
       </c>
       <c r="B35" t="n">
-        <v>91394</v>
+        <v>100451</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,37 +4576,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650798</v>
+        <v>650907</v>
       </c>
       <c r="R35" t="n">
-        <v>6672223</v>
+        <v>6672335</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4656,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4666,7 +4649,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4693,10 +4676,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393650</v>
+        <v>122393619</v>
       </c>
       <c r="B36" t="n">
-        <v>100441</v>
+        <v>90789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4705,42 +4688,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650527</v>
+        <v>650561</v>
       </c>
       <c r="R36" t="n">
-        <v>6671884</v>
+        <v>6671937</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4772,7 +4754,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4782,7 +4764,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4809,10 +4791,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393643</v>
+        <v>122393669</v>
       </c>
       <c r="B37" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4821,42 +4803,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650851</v>
+        <v>650502</v>
       </c>
       <c r="R37" t="n">
-        <v>6672282</v>
+        <v>6671865</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4888,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4898,7 +4888,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4925,10 +4915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393642</v>
+        <v>122393577</v>
       </c>
       <c r="B38" t="n">
-        <v>100441</v>
+        <v>5173</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4941,38 +4931,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650888</v>
+        <v>650572</v>
       </c>
       <c r="R38" t="n">
-        <v>6672343</v>
+        <v>6671983</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5004,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5014,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5041,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393644</v>
+        <v>122393587</v>
       </c>
       <c r="B39" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5053,42 +5048,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650753</v>
+        <v>650580</v>
       </c>
       <c r="R39" t="n">
-        <v>6672196</v>
+        <v>6671917</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5120,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5130,7 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5153,14 +5152,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393604</v>
       </c>
       <c r="B40" t="n">
-        <v>57744</v>
+        <v>57527</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5169,30 +5172,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5205,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650559</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6671894</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5240,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5250,7 +5253,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5273,14 +5281,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393669</v>
+        <v>122393605</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5289,20 +5301,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5317,25 +5329,21 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650502</v>
+        <v>650566</v>
       </c>
       <c r="R41" t="n">
-        <v>6671865</v>
+        <v>6671827</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5364,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5374,7 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5397,7 +5405,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393599</v>
+        <v>122393583</v>
       </c>
       <c r="B2" t="n">
         <v>57390</v>
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650684</v>
+        <v>650841</v>
       </c>
       <c r="R2" t="n">
-        <v>6672094</v>
+        <v>6672286</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393624</v>
+        <v>122393670</v>
       </c>
       <c r="B3" t="n">
-        <v>91404</v>
+        <v>90559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650798</v>
+        <v>650673</v>
       </c>
       <c r="R3" t="n">
-        <v>6672223</v>
+        <v>6672256</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393589</v>
+        <v>122393585</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650540</v>
+        <v>650587</v>
       </c>
       <c r="R4" t="n">
-        <v>6671903</v>
+        <v>6671916</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393598</v>
+        <v>122393610</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,50 +1050,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650520</v>
+        <v>650579</v>
       </c>
       <c r="R5" t="n">
-        <v>6671866</v>
+        <v>6671979</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1125,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393583</v>
+        <v>122393643</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1165,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650841</v>
+        <v>650851</v>
       </c>
       <c r="R6" t="n">
-        <v>6672286</v>
+        <v>6672282</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1249,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393579</v>
+        <v>122393642</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>100451</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,43 +1285,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650568</v>
+        <v>650888</v>
       </c>
       <c r="R7" t="n">
-        <v>6671816</v>
+        <v>6672343</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1370,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393649</v>
+        <v>122393589</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,31 +1397,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1451,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650513</v>
+        <v>650540</v>
       </c>
       <c r="R8" t="n">
-        <v>6671875</v>
+        <v>6671903</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1486,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393628</v>
+        <v>122393647</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,37 +1521,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1575,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650517</v>
+        <v>650531</v>
       </c>
       <c r="R9" t="n">
-        <v>6671888</v>
+        <v>6671845</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1610,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393617</v>
+        <v>122393635</v>
       </c>
       <c r="B10" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,41 +1637,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650568</v>
+        <v>650861</v>
       </c>
       <c r="R10" t="n">
-        <v>6671929</v>
+        <v>6672364</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1725,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393622</v>
+        <v>122393634</v>
       </c>
       <c r="B11" t="n">
-        <v>91182</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,36 +1753,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650619</v>
+        <v>650818</v>
       </c>
       <c r="R11" t="n">
-        <v>6671913</v>
+        <v>6672400</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1835,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,7 +1857,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393650</v>
+        <v>122393651</v>
       </c>
       <c r="B12" t="n">
         <v>100451</v>
@@ -1916,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650527</v>
+        <v>650521</v>
       </c>
       <c r="R12" t="n">
-        <v>6671884</v>
+        <v>6671872</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1951,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393623</v>
+        <v>122393637</v>
       </c>
       <c r="B13" t="n">
-        <v>91404</v>
+        <v>100451</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,37 +1989,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650805</v>
+        <v>650982</v>
       </c>
       <c r="R13" t="n">
-        <v>6672392</v>
+        <v>6672324</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2066,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122390399</v>
+        <v>122393636</v>
       </c>
       <c r="B14" t="n">
-        <v>57744</v>
+        <v>100451</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,45 +2105,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650718</v>
+        <v>650878</v>
       </c>
       <c r="R14" t="n">
-        <v>6672218</v>
+        <v>6672405</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2178,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,18 +2201,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393614</v>
+        <v>122393653</v>
       </c>
       <c r="B15" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2239,41 +2217,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650587</v>
+        <v>650726</v>
       </c>
       <c r="R15" t="n">
-        <v>6671907</v>
+        <v>6672208</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2305,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2315,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393670</v>
+        <v>122393644</v>
       </c>
       <c r="B16" t="n">
-        <v>90559</v>
+        <v>100451</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,26 +2337,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2385,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650673</v>
+        <v>650753</v>
       </c>
       <c r="R16" t="n">
-        <v>6672256</v>
+        <v>6672196</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2420,7 +2400,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393651</v>
+        <v>122393623</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
+        <v>91404</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,38 +2453,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650521</v>
+        <v>650805</v>
       </c>
       <c r="R17" t="n">
-        <v>6671872</v>
+        <v>6672392</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2536,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393653</v>
+        <v>122390399</v>
       </c>
       <c r="B18" t="n">
-        <v>100451</v>
+        <v>57744</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,27 +2568,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2617,13 +2600,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650726</v>
+        <v>650718</v>
       </c>
       <c r="R18" t="n">
-        <v>6672208</v>
+        <v>6672218</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2652,7 +2635,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2645,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,14 +2668,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393654</v>
+        <v>122393624</v>
       </c>
       <c r="B19" t="n">
-        <v>105290</v>
+        <v>91404</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,42 +2692,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650496</v>
+        <v>650798</v>
       </c>
       <c r="R19" t="n">
-        <v>6671860</v>
+        <v>6672223</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2772,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2782,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2809,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393642</v>
+        <v>122393614</v>
       </c>
       <c r="B20" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,42 +2803,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650888</v>
+        <v>650587</v>
       </c>
       <c r="R20" t="n">
-        <v>6672343</v>
+        <v>6671907</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2888,7 +2869,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2879,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393646</v>
+        <v>122393598</v>
       </c>
       <c r="B21" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,31 +2918,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2969,10 +2958,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650560</v>
+        <v>650520</v>
       </c>
       <c r="R21" t="n">
-        <v>6671817</v>
+        <v>6671866</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3004,7 +2993,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3014,7 +3003,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3041,10 +3030,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393632</v>
+        <v>122393622</v>
       </c>
       <c r="B22" t="n">
-        <v>100451</v>
+        <v>91182</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,42 +3042,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650791</v>
+        <v>650619</v>
       </c>
       <c r="R22" t="n">
-        <v>6672382</v>
+        <v>6671913</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3120,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3130,7 +3113,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393578</v>
+        <v>122393632</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>100451</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3173,43 +3156,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650620</v>
+        <v>650791</v>
       </c>
       <c r="R23" t="n">
-        <v>6671917</v>
+        <v>6672382</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3241,7 +3219,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3229,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393610</v>
+        <v>122393619</v>
       </c>
       <c r="B24" t="n">
-        <v>90754</v>
+        <v>90789</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3290,25 +3268,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3321,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650579</v>
+        <v>650561</v>
       </c>
       <c r="R24" t="n">
-        <v>6671979</v>
+        <v>6671937</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3356,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3366,7 +3344,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3393,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393635</v>
+        <v>122393611</v>
       </c>
       <c r="B25" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3405,42 +3383,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650861</v>
+        <v>650587</v>
       </c>
       <c r="R25" t="n">
-        <v>6672364</v>
+        <v>6671963</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3472,7 +3449,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3482,7 +3459,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3509,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393637</v>
+        <v>122393649</v>
       </c>
       <c r="B26" t="n">
         <v>100451</v>
@@ -3549,14 +3526,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650982</v>
+        <v>650513</v>
       </c>
       <c r="R26" t="n">
-        <v>6672324</v>
+        <v>6671875</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3588,7 +3565,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3598,7 +3575,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,10 +3602,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393636</v>
+        <v>122393617</v>
       </c>
       <c r="B27" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3637,42 +3614,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650878</v>
+        <v>650568</v>
       </c>
       <c r="R27" t="n">
-        <v>6672405</v>
+        <v>6671929</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3704,7 +3680,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3714,7 +3690,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3741,10 +3717,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393585</v>
+        <v>122393578</v>
       </c>
       <c r="B28" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3753,20 +3729,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3774,16 +3750,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3793,10 +3766,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650587</v>
+        <v>650620</v>
       </c>
       <c r="R28" t="n">
-        <v>6671916</v>
+        <v>6671917</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3828,7 +3801,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,7 +3811,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3865,10 +3838,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393634</v>
+        <v>122393599</v>
       </c>
       <c r="B29" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3877,42 +3850,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650818</v>
+        <v>650684</v>
       </c>
       <c r="R29" t="n">
-        <v>6672400</v>
+        <v>6672094</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3944,7 +3925,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3954,7 +3935,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3981,10 +3962,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393633</v>
+        <v>122393669</v>
       </c>
       <c r="B30" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3993,42 +3974,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650806</v>
+        <v>650502</v>
       </c>
       <c r="R30" t="n">
-        <v>6672399</v>
+        <v>6671865</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4060,7 +4049,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,7 +4059,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4086,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393611</v>
+        <v>122393650</v>
       </c>
       <c r="B31" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4109,41 +4098,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650587</v>
+        <v>650527</v>
       </c>
       <c r="R31" t="n">
-        <v>6671963</v>
+        <v>6671884</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4175,7 +4165,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4185,7 +4175,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4212,10 +4202,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393643</v>
+        <v>122393577</v>
       </c>
       <c r="B32" t="n">
-        <v>100451</v>
+        <v>5173</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4228,27 +4218,32 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650851</v>
+        <v>650572</v>
       </c>
       <c r="R32" t="n">
-        <v>6672282</v>
+        <v>6671983</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4328,10 +4323,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393647</v>
+        <v>122393628</v>
       </c>
       <c r="B33" t="n">
-        <v>100451</v>
+        <v>98185</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4340,29 +4335,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4372,10 +4375,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650531</v>
+        <v>650517</v>
       </c>
       <c r="R33" t="n">
-        <v>6671845</v>
+        <v>6671888</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4407,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4417,7 +4420,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4444,7 +4447,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393644</v>
+        <v>122393646</v>
       </c>
       <c r="B34" t="n">
         <v>100451</v>
@@ -4484,14 +4487,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650753</v>
+        <v>650560</v>
       </c>
       <c r="R34" t="n">
-        <v>6672196</v>
+        <v>6671817</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4523,7 +4526,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4533,7 +4536,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4560,10 +4563,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393640</v>
+        <v>122393654</v>
       </c>
       <c r="B35" t="n">
-        <v>100451</v>
+        <v>105290</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4576,38 +4579,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650907</v>
+        <v>650496</v>
       </c>
       <c r="R35" t="n">
-        <v>6672335</v>
+        <v>6671860</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4639,7 +4646,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,7 +4656,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4676,10 +4683,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393619</v>
+        <v>122393640</v>
       </c>
       <c r="B36" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4688,41 +4695,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650561</v>
+        <v>650907</v>
       </c>
       <c r="R36" t="n">
-        <v>6671937</v>
+        <v>6672335</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4754,7 +4762,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4764,7 +4772,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4791,10 +4799,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393669</v>
+        <v>122393633</v>
       </c>
       <c r="B37" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4803,50 +4811,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650502</v>
+        <v>650806</v>
       </c>
       <c r="R37" t="n">
-        <v>6671865</v>
+        <v>6672399</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393577</v>
+        <v>122393579</v>
       </c>
       <c r="B38" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4954,20 +4954,20 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650572</v>
+        <v>650568</v>
       </c>
       <c r="R38" t="n">
-        <v>6671983</v>
+        <v>6671816</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B39" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5052,26 +5052,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R39" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5165,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B40" t="n">
-        <v>57527</v>
+        <v>57744</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,30 +5177,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5208,13 +5213,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R40" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,12 +5258,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B41" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5301,20 +5301,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R41" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S41" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -2321,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393644</v>
+        <v>122393623</v>
       </c>
       <c r="B16" t="n">
-        <v>100451</v>
+        <v>91404</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,38 +2337,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650753</v>
+        <v>650805</v>
       </c>
       <c r="R16" t="n">
-        <v>6672196</v>
+        <v>6672392</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2400,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2409,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393623</v>
+        <v>122393644</v>
       </c>
       <c r="B17" t="n">
-        <v>91404</v>
+        <v>100451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,37 +2452,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650805</v>
+        <v>650753</v>
       </c>
       <c r="R17" t="n">
-        <v>6672392</v>
+        <v>6672196</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122390399</v>
+        <v>122393624</v>
       </c>
       <c r="B18" t="n">
-        <v>57744</v>
+        <v>91404</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2568,31 +2568,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2600,13 +2595,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650718</v>
+        <v>650798</v>
       </c>
       <c r="R18" t="n">
-        <v>6672218</v>
+        <v>6672223</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2635,7 +2630,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2645,7 +2640,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,18 +2663,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393624</v>
+        <v>122393614</v>
       </c>
       <c r="B19" t="n">
-        <v>91404</v>
+        <v>90789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,25 +2679,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,14 +2706,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650798</v>
+        <v>650587</v>
       </c>
       <c r="R19" t="n">
-        <v>6672223</v>
+        <v>6671907</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2754,7 +2745,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2755,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393614</v>
+        <v>122390399</v>
       </c>
       <c r="B20" t="n">
-        <v>90789</v>
+        <v>57744</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,44 +2794,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650587</v>
+        <v>650718</v>
       </c>
       <c r="R20" t="n">
-        <v>6671907</v>
+        <v>6672218</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2869,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2879,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,7 +2898,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393632</v>
+        <v>122393619</v>
       </c>
       <c r="B23" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,42 +3152,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650791</v>
+        <v>650561</v>
       </c>
       <c r="R23" t="n">
-        <v>6672382</v>
+        <v>6671937</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3219,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3229,7 +3228,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,7 +3255,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393619</v>
+        <v>122393611</v>
       </c>
       <c r="B24" t="n">
         <v>90789</v>
@@ -3299,10 +3298,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650561</v>
+        <v>650587</v>
       </c>
       <c r="R24" t="n">
-        <v>6671937</v>
+        <v>6671963</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3334,7 +3333,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3344,7 +3343,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3371,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393611</v>
+        <v>122393632</v>
       </c>
       <c r="B25" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3383,41 +3382,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650587</v>
+        <v>650791</v>
       </c>
       <c r="R25" t="n">
-        <v>6671963</v>
+        <v>6672382</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393669</v>
+        <v>122393650</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3974,50 +3974,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650502</v>
+        <v>650527</v>
       </c>
       <c r="R30" t="n">
-        <v>6671865</v>
+        <v>6671884</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4049,7 +4041,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4059,7 +4051,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,10 +4078,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393650</v>
+        <v>122393669</v>
       </c>
       <c r="B31" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4098,42 +4090,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650527</v>
+        <v>650502</v>
       </c>
       <c r="R31" t="n">
-        <v>6671884</v>
+        <v>6671865</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393583</v>
+        <v>122393635</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650841</v>
+        <v>650861</v>
       </c>
       <c r="R2" t="n">
-        <v>6672286</v>
+        <v>6672364</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393670</v>
+        <v>122393632</v>
       </c>
       <c r="B3" t="n">
-        <v>90559</v>
+        <v>100463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,37 +807,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650673</v>
+        <v>650791</v>
       </c>
       <c r="R3" t="n">
-        <v>6672256</v>
+        <v>6672382</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393585</v>
+        <v>122393619</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,46 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650587</v>
+        <v>650561</v>
       </c>
       <c r="R4" t="n">
-        <v>6671916</v>
+        <v>6671937</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393610</v>
+        <v>122393577</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,26 +1038,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650579</v>
+        <v>650572</v>
       </c>
       <c r="R5" t="n">
-        <v>6671979</v>
+        <v>6671983</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393643</v>
+        <v>122393599</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,31 +1155,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650851</v>
+        <v>650684</v>
       </c>
       <c r="R6" t="n">
-        <v>6672282</v>
+        <v>6672094</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1232,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393642</v>
+        <v>122393598</v>
       </c>
       <c r="B7" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,42 +1279,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650888</v>
+        <v>650520</v>
       </c>
       <c r="R7" t="n">
-        <v>6672343</v>
+        <v>6671866</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1348,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393589</v>
+        <v>122393649</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,39 +1403,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1437,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650540</v>
+        <v>650513</v>
       </c>
       <c r="R8" t="n">
-        <v>6671903</v>
+        <v>6671875</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1472,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393647</v>
+        <v>122393654</v>
       </c>
       <c r="B9" t="n">
-        <v>100451</v>
+        <v>105303</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,38 +1523,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650531</v>
+        <v>650496</v>
       </c>
       <c r="R9" t="n">
-        <v>6671845</v>
+        <v>6671860</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1588,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1600,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393635</v>
+        <v>122393624</v>
       </c>
       <c r="B10" t="n">
-        <v>100451</v>
+        <v>91416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,38 +1643,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650861</v>
+        <v>650798</v>
       </c>
       <c r="R10" t="n">
-        <v>6672364</v>
+        <v>6672223</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1704,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393634</v>
+        <v>122393614</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
+        <v>90801</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,42 +1754,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650818</v>
+        <v>650587</v>
       </c>
       <c r="R11" t="n">
-        <v>6672400</v>
+        <v>6671907</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393651</v>
+        <v>122393643</v>
       </c>
       <c r="B12" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,14 +1897,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650521</v>
+        <v>650851</v>
       </c>
       <c r="R12" t="n">
-        <v>6671872</v>
+        <v>6672282</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393637</v>
+        <v>122393634</v>
       </c>
       <c r="B13" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,14 +2013,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650982</v>
+        <v>650818</v>
       </c>
       <c r="R13" t="n">
-        <v>6672324</v>
+        <v>6672400</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393636</v>
+        <v>122393578</v>
       </c>
       <c r="B14" t="n">
-        <v>100451</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,38 +2105,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650878</v>
+        <v>650620</v>
       </c>
       <c r="R14" t="n">
-        <v>6672405</v>
+        <v>6671917</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2168,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393653</v>
+        <v>122393611</v>
       </c>
       <c r="B15" t="n">
-        <v>100451</v>
+        <v>90801</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,31 +2222,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2249,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650726</v>
+        <v>650587</v>
       </c>
       <c r="R15" t="n">
-        <v>6672208</v>
+        <v>6671963</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2284,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393623</v>
+        <v>122393637</v>
       </c>
       <c r="B16" t="n">
-        <v>91404</v>
+        <v>100463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,37 +2341,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650805</v>
+        <v>650982</v>
       </c>
       <c r="R16" t="n">
-        <v>6672392</v>
+        <v>6672324</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2399,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2409,7 +2414,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393644</v>
+        <v>122393646</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,14 +2481,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650753</v>
+        <v>650560</v>
       </c>
       <c r="R17" t="n">
-        <v>6672196</v>
+        <v>6671817</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2515,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393624</v>
+        <v>122393670</v>
       </c>
       <c r="B18" t="n">
-        <v>91404</v>
+        <v>90571</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2568,21 +2573,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2595,10 +2600,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650798</v>
+        <v>650673</v>
       </c>
       <c r="R18" t="n">
-        <v>6672223</v>
+        <v>6672256</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2630,7 +2635,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2640,7 +2645,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393614</v>
+        <v>122393633</v>
       </c>
       <c r="B19" t="n">
-        <v>90789</v>
+        <v>100463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,41 +2684,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650587</v>
+        <v>650806</v>
       </c>
       <c r="R19" t="n">
-        <v>6671907</v>
+        <v>6672399</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2745,7 +2751,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2761,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122390399</v>
+        <v>122393647</v>
       </c>
       <c r="B20" t="n">
-        <v>57744</v>
+        <v>100463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,45 +2804,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650718</v>
+        <v>650531</v>
       </c>
       <c r="R20" t="n">
-        <v>6672218</v>
+        <v>6671845</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2865,7 +2867,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2877,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,18 +2900,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393598</v>
+        <v>122393579</v>
       </c>
       <c r="B21" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,20 +2916,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2939,16 +2937,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2958,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650520</v>
+        <v>650568</v>
       </c>
       <c r="R21" t="n">
-        <v>6671866</v>
+        <v>6671816</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2993,7 +2988,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3003,7 +2998,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3030,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393622</v>
+        <v>122393617</v>
       </c>
       <c r="B22" t="n">
-        <v>91182</v>
+        <v>90801</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3046,16 +3041,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3064,14 +3064,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650619</v>
+        <v>650568</v>
       </c>
       <c r="R22" t="n">
-        <v>6671913</v>
+        <v>6671929</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393619</v>
+        <v>122393585</v>
       </c>
       <c r="B23" t="n">
-        <v>90789</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,37 +3156,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650561</v>
+        <v>650587</v>
       </c>
       <c r="R23" t="n">
-        <v>6671937</v>
+        <v>6671916</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3218,7 +3227,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,7 +3237,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3255,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393611</v>
+        <v>122393651</v>
       </c>
       <c r="B24" t="n">
-        <v>90789</v>
+        <v>100463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3267,41 +3276,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650587</v>
+        <v>650521</v>
       </c>
       <c r="R24" t="n">
-        <v>6671963</v>
+        <v>6671872</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3333,7 +3343,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3343,7 +3353,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3370,10 +3380,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393632</v>
+        <v>122393622</v>
       </c>
       <c r="B25" t="n">
-        <v>100451</v>
+        <v>91194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3382,42 +3392,36 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650791</v>
+        <v>650619</v>
       </c>
       <c r="R25" t="n">
-        <v>6672382</v>
+        <v>6671913</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3449,7 +3453,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3459,7 +3463,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,10 +3490,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393649</v>
+        <v>122393650</v>
       </c>
       <c r="B26" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650513</v>
+        <v>650527</v>
       </c>
       <c r="R26" t="n">
-        <v>6671875</v>
+        <v>6671884</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3565,7 +3569,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3602,10 +3606,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393617</v>
+        <v>122393583</v>
       </c>
       <c r="B27" t="n">
-        <v>90789</v>
+        <v>57395</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3618,26 +3622,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3645,10 +3658,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650568</v>
+        <v>650841</v>
       </c>
       <c r="R27" t="n">
-        <v>6671929</v>
+        <v>6672286</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3680,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3690,7 +3703,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3717,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393578</v>
+        <v>122390399</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>57749</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,16 +3746,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3750,29 +3763,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650620</v>
+        <v>650718</v>
       </c>
       <c r="R28" t="n">
-        <v>6671917</v>
+        <v>6672218</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3801,7 +3813,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3811,7 +3823,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3834,14 +3846,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393599</v>
+        <v>122393628</v>
       </c>
       <c r="B29" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3850,50 +3866,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650684</v>
+        <v>650517</v>
       </c>
       <c r="R29" t="n">
-        <v>6672094</v>
+        <v>6671888</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3925,7 +3941,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3935,7 +3951,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,10 +3978,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393650</v>
+        <v>122393653</v>
       </c>
       <c r="B30" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4002,14 +4018,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650527</v>
+        <v>650726</v>
       </c>
       <c r="R30" t="n">
-        <v>6671884</v>
+        <v>6672208</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4041,7 +4057,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4051,7 +4067,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4078,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393669</v>
+        <v>122393642</v>
       </c>
       <c r="B31" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4090,50 +4106,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650502</v>
+        <v>650888</v>
       </c>
       <c r="R31" t="n">
-        <v>6671865</v>
+        <v>6672343</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4165,7 +4173,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4175,7 +4183,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4202,10 +4210,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393577</v>
+        <v>122393644</v>
       </c>
       <c r="B32" t="n">
-        <v>5173</v>
+        <v>100463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4218,32 +4226,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4251,10 +4254,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650572</v>
+        <v>650753</v>
       </c>
       <c r="R32" t="n">
-        <v>6671983</v>
+        <v>6672196</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4286,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4296,7 +4299,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4323,10 +4326,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393628</v>
+        <v>122393610</v>
       </c>
       <c r="B33" t="n">
-        <v>98185</v>
+        <v>90766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4335,50 +4338,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650517</v>
+        <v>650579</v>
       </c>
       <c r="R33" t="n">
-        <v>6671888</v>
+        <v>6671979</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4410,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,7 +4414,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4447,10 +4441,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393646</v>
+        <v>122393589</v>
       </c>
       <c r="B34" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4459,31 +4453,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4491,10 +4493,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650560</v>
+        <v>650540</v>
       </c>
       <c r="R34" t="n">
-        <v>6671817</v>
+        <v>6671903</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4526,7 +4528,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4536,7 +4538,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4563,10 +4565,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393654</v>
+        <v>122393636</v>
       </c>
       <c r="B35" t="n">
-        <v>105290</v>
+        <v>100463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4579,42 +4581,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650496</v>
+        <v>650878</v>
       </c>
       <c r="R35" t="n">
-        <v>6671860</v>
+        <v>6672405</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4646,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4656,7 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4683,10 +4681,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393640</v>
+        <v>122393669</v>
       </c>
       <c r="B36" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4695,42 +4693,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650907</v>
+        <v>650502</v>
       </c>
       <c r="R36" t="n">
-        <v>6672335</v>
+        <v>6671865</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4762,7 +4768,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4772,7 +4778,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4799,10 +4805,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393633</v>
+        <v>122393640</v>
       </c>
       <c r="B37" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4839,14 +4845,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650806</v>
+        <v>650907</v>
       </c>
       <c r="R37" t="n">
-        <v>6672399</v>
+        <v>6672335</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4878,7 +4884,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,7 +4894,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4915,10 +4921,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393579</v>
+        <v>122393623</v>
       </c>
       <c r="B38" t="n">
-        <v>5193</v>
+        <v>91416</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4931,43 +4937,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650568</v>
+        <v>650805</v>
       </c>
       <c r="R38" t="n">
-        <v>6671816</v>
+        <v>6672392</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B39" t="n">
-        <v>57527</v>
+        <v>57749</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,30 +5048,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R39" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S39" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,12 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5165,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393604</v>
       </c>
       <c r="B40" t="n">
-        <v>57744</v>
+        <v>57532</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5177,30 +5172,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5213,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650559</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6671894</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5258,7 +5253,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5292,7 +5292,7 @@
         <v>122393587</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393635</v>
+        <v>122393598</v>
       </c>
       <c r="B2" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650861</v>
+        <v>650520</v>
       </c>
       <c r="R2" t="n">
-        <v>6672364</v>
+        <v>6671866</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393632</v>
+        <v>122393646</v>
       </c>
       <c r="B3" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,14 +839,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650791</v>
+        <v>650560</v>
       </c>
       <c r="R3" t="n">
-        <v>6672382</v>
+        <v>6671817</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393619</v>
+        <v>122393634</v>
       </c>
       <c r="B4" t="n">
-        <v>90801</v>
+        <v>100468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,41 +927,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650561</v>
+        <v>650818</v>
       </c>
       <c r="R4" t="n">
-        <v>6671937</v>
+        <v>6672400</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393577</v>
+        <v>122393632</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>100468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,43 +1047,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650572</v>
+        <v>650791</v>
       </c>
       <c r="R5" t="n">
-        <v>6671983</v>
+        <v>6672382</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393599</v>
+        <v>122393583</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1185,7 +1189,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1195,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650684</v>
+        <v>650841</v>
       </c>
       <c r="R6" t="n">
-        <v>6672094</v>
+        <v>6672286</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393598</v>
+        <v>122393577</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,50 +1283,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650520</v>
+        <v>650572</v>
       </c>
       <c r="R7" t="n">
-        <v>6671866</v>
+        <v>6671983</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1354,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393649</v>
+        <v>122393578</v>
       </c>
       <c r="B8" t="n">
-        <v>100463</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,27 +1408,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650513</v>
+        <v>650620</v>
       </c>
       <c r="R8" t="n">
-        <v>6671875</v>
+        <v>6671917</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1470,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393654</v>
+        <v>122393669</v>
       </c>
       <c r="B9" t="n">
-        <v>105303</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,35 +1525,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650496</v>
+        <v>650502</v>
       </c>
       <c r="R9" t="n">
-        <v>6671860</v>
+        <v>6671865</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1590,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393624</v>
+        <v>122393653</v>
       </c>
       <c r="B10" t="n">
-        <v>91416</v>
+        <v>100468</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,26 +1653,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650798</v>
+        <v>650726</v>
       </c>
       <c r="R10" t="n">
-        <v>6672223</v>
+        <v>6672208</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1705,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393614</v>
+        <v>122393623</v>
       </c>
       <c r="B11" t="n">
-        <v>90801</v>
+        <v>91421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1765,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1781,14 +1792,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650587</v>
+        <v>650805</v>
       </c>
       <c r="R11" t="n">
-        <v>6671907</v>
+        <v>6672392</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1820,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393643</v>
+        <v>122393651</v>
       </c>
       <c r="B12" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,14 +1908,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650851</v>
+        <v>650521</v>
       </c>
       <c r="R12" t="n">
-        <v>6672282</v>
+        <v>6671872</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1936,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393634</v>
+        <v>122393589</v>
       </c>
       <c r="B13" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,42 +1996,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650818</v>
+        <v>650540</v>
       </c>
       <c r="R13" t="n">
-        <v>6672400</v>
+        <v>6671903</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2052,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393578</v>
+        <v>122393633</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>100468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,43 +2124,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650620</v>
+        <v>650806</v>
       </c>
       <c r="R14" t="n">
-        <v>6671917</v>
+        <v>6672399</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2173,7 +2187,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2183,7 +2197,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393611</v>
+        <v>122393642</v>
       </c>
       <c r="B15" t="n">
-        <v>90801</v>
+        <v>100468</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,41 +2236,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650587</v>
+        <v>650888</v>
       </c>
       <c r="R15" t="n">
-        <v>6671963</v>
+        <v>6672343</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2288,7 +2303,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2313,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,10 +2340,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393637</v>
+        <v>122393585</v>
       </c>
       <c r="B16" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,42 +2352,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650982</v>
+        <v>650587</v>
       </c>
       <c r="R16" t="n">
-        <v>6672324</v>
+        <v>6671916</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2404,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2437,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393646</v>
+        <v>122393610</v>
       </c>
       <c r="B17" t="n">
-        <v>100463</v>
+        <v>90773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,38 +2480,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650560</v>
+        <v>650579</v>
       </c>
       <c r="R17" t="n">
-        <v>6671817</v>
+        <v>6671979</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2520,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2552,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393670</v>
+        <v>122393635</v>
       </c>
       <c r="B18" t="n">
-        <v>90571</v>
+        <v>100468</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,37 +2595,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650673</v>
+        <v>650861</v>
       </c>
       <c r="R18" t="n">
-        <v>6672256</v>
+        <v>6672364</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2635,7 +2658,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2645,7 +2668,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393633</v>
+        <v>122393650</v>
       </c>
       <c r="B19" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,14 +2735,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650806</v>
+        <v>650527</v>
       </c>
       <c r="R19" t="n">
-        <v>6672399</v>
+        <v>6671884</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2751,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,7 +2784,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393647</v>
+        <v>122393579</v>
       </c>
       <c r="B20" t="n">
-        <v>100463</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,27 +2827,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2832,10 +2860,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650531</v>
+        <v>650568</v>
       </c>
       <c r="R20" t="n">
-        <v>6671845</v>
+        <v>6671816</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2867,7 +2895,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2877,7 +2905,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2904,10 +2932,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393579</v>
+        <v>122393617</v>
       </c>
       <c r="B21" t="n">
-        <v>5193</v>
+        <v>90808</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,47 +2944,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>650568</v>
       </c>
       <c r="R21" t="n">
-        <v>6671816</v>
+        <v>6671929</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2988,7 +3010,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2998,7 +3020,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3025,10 +3047,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393617</v>
+        <v>122393654</v>
       </c>
       <c r="B22" t="n">
-        <v>90801</v>
+        <v>105308</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,41 +3059,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650568</v>
+        <v>650496</v>
       </c>
       <c r="R22" t="n">
-        <v>6671929</v>
+        <v>6671860</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3103,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3113,7 +3140,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3140,10 +3167,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393585</v>
+        <v>122393624</v>
       </c>
       <c r="B23" t="n">
-        <v>57395</v>
+        <v>91421</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,50 +3179,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650587</v>
+        <v>650798</v>
       </c>
       <c r="R23" t="n">
-        <v>6671916</v>
+        <v>6672223</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3227,7 +3245,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3237,7 +3255,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,10 +3282,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393651</v>
+        <v>122393614</v>
       </c>
       <c r="B24" t="n">
-        <v>100463</v>
+        <v>90808</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3276,31 +3294,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3308,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650521</v>
+        <v>650587</v>
       </c>
       <c r="R24" t="n">
-        <v>6671872</v>
+        <v>6671907</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3343,7 +3360,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3353,7 +3370,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3380,10 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393622</v>
+        <v>122393644</v>
       </c>
       <c r="B25" t="n">
-        <v>91194</v>
+        <v>100468</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3392,36 +3409,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650619</v>
+        <v>650753</v>
       </c>
       <c r="R25" t="n">
-        <v>6671913</v>
+        <v>6672196</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3453,7 +3476,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3463,7 +3486,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3490,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393650</v>
+        <v>122393649</v>
       </c>
       <c r="B26" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3534,10 +3557,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650527</v>
+        <v>650513</v>
       </c>
       <c r="R26" t="n">
-        <v>6671884</v>
+        <v>6671875</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3569,7 +3592,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3579,7 +3602,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,10 +3629,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393583</v>
+        <v>122393647</v>
       </c>
       <c r="B27" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3618,50 +3641,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650841</v>
+        <v>650531</v>
       </c>
       <c r="R27" t="n">
-        <v>6672286</v>
+        <v>6671845</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3693,7 +3708,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3703,7 +3718,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,10 +3745,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122390399</v>
+        <v>122393622</v>
       </c>
       <c r="B28" t="n">
-        <v>57749</v>
+        <v>91199</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3742,49 +3757,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650718</v>
+        <v>650619</v>
       </c>
       <c r="R28" t="n">
-        <v>6672218</v>
+        <v>6671913</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3813,7 +3818,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3823,7 +3828,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,18 +3851,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393628</v>
+        <v>122393611</v>
       </c>
       <c r="B29" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3866,50 +3867,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650517</v>
+        <v>650587</v>
       </c>
       <c r="R29" t="n">
-        <v>6671888</v>
+        <v>6671963</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3941,7 +3933,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3951,7 +3943,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3978,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393653</v>
+        <v>122393640</v>
       </c>
       <c r="B30" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4018,14 +4010,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650726</v>
+        <v>650907</v>
       </c>
       <c r="R30" t="n">
-        <v>6672208</v>
+        <v>6672335</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4057,7 +4049,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4067,7 +4059,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,10 +4086,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393642</v>
+        <v>122393636</v>
       </c>
       <c r="B31" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4134,14 +4126,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650888</v>
+        <v>650878</v>
       </c>
       <c r="R31" t="n">
-        <v>6672343</v>
+        <v>6672405</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4173,7 +4165,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4183,7 +4175,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4210,10 +4202,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393644</v>
+        <v>122390399</v>
       </c>
       <c r="B32" t="n">
-        <v>100463</v>
+        <v>57749</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4226,27 +4218,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4254,13 +4250,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650753</v>
+        <v>650718</v>
       </c>
       <c r="R32" t="n">
-        <v>6672196</v>
+        <v>6672218</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4289,7 +4285,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,7 +4295,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4322,14 +4318,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393610</v>
+        <v>122393619</v>
       </c>
       <c r="B33" t="n">
-        <v>90766</v>
+        <v>90808</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4338,25 +4338,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650579</v>
+        <v>650561</v>
       </c>
       <c r="R33" t="n">
-        <v>6671979</v>
+        <v>6671937</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4441,10 +4441,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393589</v>
+        <v>122393628</v>
       </c>
       <c r="B34" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,39 +4453,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650540</v>
+        <v>650517</v>
       </c>
       <c r="R34" t="n">
-        <v>6671903</v>
+        <v>6671888</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4565,10 +4565,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393636</v>
+        <v>122393599</v>
       </c>
       <c r="B35" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4577,42 +4577,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650878</v>
+        <v>650684</v>
       </c>
       <c r="R35" t="n">
-        <v>6672405</v>
+        <v>6672094</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4644,7 +4652,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4654,7 +4662,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,10 +4689,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393669</v>
+        <v>122393637</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4693,50 +4701,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650502</v>
+        <v>650982</v>
       </c>
       <c r="R36" t="n">
-        <v>6671865</v>
+        <v>6672324</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4805,10 +4805,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393640</v>
+        <v>122393643</v>
       </c>
       <c r="B37" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4845,14 +4845,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650907</v>
+        <v>650851</v>
       </c>
       <c r="R37" t="n">
-        <v>6672335</v>
+        <v>6672282</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,10 +4921,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393623</v>
+        <v>122393670</v>
       </c>
       <c r="B38" t="n">
-        <v>91416</v>
+        <v>90575</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4960,14 +4960,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650805</v>
+        <v>650673</v>
       </c>
       <c r="R38" t="n">
-        <v>6672392</v>
+        <v>6672256</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B39" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,20 +5048,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R39" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B40" t="n">
-        <v>57532</v>
+        <v>57749</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,30 +5172,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R40" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,12 +5253,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,10 +5284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5305,26 +5300,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5337,13 +5332,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R41" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,7 +5377,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393669</v>
+        <v>122393653</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,50 +1525,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650502</v>
+        <v>650726</v>
       </c>
       <c r="R9" t="n">
-        <v>6671865</v>
+        <v>6672208</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1600,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393653</v>
+        <v>122393669</v>
       </c>
       <c r="B10" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,42 +1641,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650726</v>
+        <v>650502</v>
       </c>
       <c r="R10" t="n">
-        <v>6672208</v>
+        <v>6671865</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393651</v>
+        <v>122393589</v>
       </c>
       <c r="B12" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,31 +1880,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1912,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650521</v>
+        <v>650540</v>
       </c>
       <c r="R12" t="n">
-        <v>6671872</v>
+        <v>6671903</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1947,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393589</v>
+        <v>122393651</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,39 +2004,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650540</v>
+        <v>650521</v>
       </c>
       <c r="R13" t="n">
-        <v>6671903</v>
+        <v>6671872</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -4565,10 +4565,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393599</v>
+        <v>122393637</v>
       </c>
       <c r="B35" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4577,50 +4577,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650684</v>
+        <v>650982</v>
       </c>
       <c r="R35" t="n">
-        <v>6672094</v>
+        <v>6672324</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4652,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4662,7 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4689,7 +4681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393637</v>
+        <v>122393643</v>
       </c>
       <c r="B36" t="n">
         <v>100468</v>
@@ -4729,14 +4721,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650982</v>
+        <v>650851</v>
       </c>
       <c r="R36" t="n">
-        <v>6672324</v>
+        <v>6672282</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4768,7 +4760,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4778,7 +4770,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4805,10 +4797,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393643</v>
+        <v>122393599</v>
       </c>
       <c r="B37" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4817,31 +4809,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650851</v>
+        <v>650684</v>
       </c>
       <c r="R37" t="n">
-        <v>6672282</v>
+        <v>6672094</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393598</v>
+        <v>122393635</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650520</v>
+        <v>650861</v>
       </c>
       <c r="R2" t="n">
-        <v>6671866</v>
+        <v>6672364</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393646</v>
+        <v>122393610</v>
       </c>
       <c r="B3" t="n">
-        <v>100468</v>
+        <v>90778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,38 +802,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650560</v>
+        <v>650579</v>
       </c>
       <c r="R3" t="n">
-        <v>6671817</v>
+        <v>6671979</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +869,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393634</v>
+        <v>122393577</v>
       </c>
       <c r="B4" t="n">
-        <v>100468</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +912,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650818</v>
+        <v>650572</v>
       </c>
       <c r="R4" t="n">
-        <v>6672400</v>
+        <v>6671983</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393632</v>
+        <v>122393599</v>
       </c>
       <c r="B5" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,42 +1024,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650791</v>
+        <v>650684</v>
       </c>
       <c r="R5" t="n">
-        <v>6672382</v>
+        <v>6672094</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393583</v>
+        <v>122393614</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,46 +1147,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650841</v>
+        <v>650587</v>
       </c>
       <c r="R6" t="n">
-        <v>6672286</v>
+        <v>6671907</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1234,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393577</v>
+        <v>122393632</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>100477</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,43 +1257,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650572</v>
+        <v>650791</v>
       </c>
       <c r="R7" t="n">
-        <v>6671983</v>
+        <v>6672382</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1355,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393578</v>
+        <v>122393619</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>90813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,47 +1364,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650620</v>
+        <v>650561</v>
       </c>
       <c r="R8" t="n">
-        <v>6671917</v>
+        <v>6671937</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1476,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393653</v>
+        <v>122393623</v>
       </c>
       <c r="B9" t="n">
-        <v>100468</v>
+        <v>91426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,38 +1478,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>1339</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650726</v>
+        <v>650805</v>
       </c>
       <c r="R9" t="n">
-        <v>6672208</v>
+        <v>6672392</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1592,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393669</v>
+        <v>122393617</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,46 +1588,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650502</v>
+        <v>650568</v>
       </c>
       <c r="R10" t="n">
-        <v>6671865</v>
+        <v>6671929</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1716,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393623</v>
+        <v>122393669</v>
       </c>
       <c r="B11" t="n">
-        <v>91421</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,41 +1694,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650805</v>
+        <v>650502</v>
       </c>
       <c r="R11" t="n">
-        <v>6672392</v>
+        <v>6671865</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1831,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393589</v>
+        <v>122393634</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,50 +1813,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650540</v>
+        <v>650818</v>
       </c>
       <c r="R12" t="n">
-        <v>6671903</v>
+        <v>6672400</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1955,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393651</v>
+        <v>122393637</v>
       </c>
       <c r="B13" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2009,11 +1929,6 @@
       </c>
       <c r="E13" t="n">
         <v>222498</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2032,14 +1947,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650521</v>
+        <v>650982</v>
       </c>
       <c r="R13" t="n">
-        <v>6671872</v>
+        <v>6672324</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2071,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393633</v>
+        <v>122393622</v>
       </c>
       <c r="B14" t="n">
-        <v>100468</v>
+        <v>91204</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,42 +2035,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650806</v>
+        <v>650619</v>
       </c>
       <c r="R14" t="n">
-        <v>6672399</v>
+        <v>6671913</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2187,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2197,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393642</v>
+        <v>122393598</v>
       </c>
       <c r="B15" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,42 +2145,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650888</v>
+        <v>650520</v>
       </c>
       <c r="R15" t="n">
-        <v>6672343</v>
+        <v>6671866</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2303,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2313,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393585</v>
+        <v>122393578</v>
       </c>
       <c r="B16" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,20 +2264,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2373,16 +2280,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2392,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650587</v>
+        <v>650620</v>
       </c>
       <c r="R16" t="n">
-        <v>6671916</v>
+        <v>6671917</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2427,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393610</v>
+        <v>122393579</v>
       </c>
       <c r="B17" t="n">
-        <v>90773</v>
+        <v>5193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,37 +2384,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650579</v>
+        <v>650568</v>
       </c>
       <c r="R17" t="n">
-        <v>6671979</v>
+        <v>6671816</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2542,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393635</v>
+        <v>122393628</v>
       </c>
       <c r="B18" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,42 +2496,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650861</v>
+        <v>650517</v>
       </c>
       <c r="R18" t="n">
-        <v>6672364</v>
+        <v>6671888</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2658,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2668,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393650</v>
+        <v>122393646</v>
       </c>
       <c r="B19" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,11 +2620,6 @@
       </c>
       <c r="E19" t="n">
         <v>222498</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2739,10 +2642,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650527</v>
+        <v>650560</v>
       </c>
       <c r="R19" t="n">
-        <v>6671884</v>
+        <v>6671817</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2774,7 +2677,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,7 +2687,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393579</v>
+        <v>122393643</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>100477</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,43 +2730,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650568</v>
+        <v>650851</v>
       </c>
       <c r="R20" t="n">
-        <v>6671816</v>
+        <v>6672282</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2895,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2905,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393617</v>
+        <v>122393653</v>
       </c>
       <c r="B21" t="n">
-        <v>90808</v>
+        <v>100477</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2944,30 +2837,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2975,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650568</v>
+        <v>650726</v>
       </c>
       <c r="R21" t="n">
-        <v>6671929</v>
+        <v>6672208</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3010,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3020,7 +2909,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,10 +2936,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393654</v>
+        <v>122393644</v>
       </c>
       <c r="B22" t="n">
-        <v>105308</v>
+        <v>100477</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3063,42 +2952,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650496</v>
+        <v>650753</v>
       </c>
       <c r="R22" t="n">
-        <v>6671860</v>
+        <v>6672196</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3130,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393624</v>
+        <v>122393636</v>
       </c>
       <c r="B23" t="n">
-        <v>91421</v>
+        <v>100477</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3183,37 +3063,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650798</v>
+        <v>650878</v>
       </c>
       <c r="R23" t="n">
-        <v>6672223</v>
+        <v>6672405</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3245,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3255,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393614</v>
+        <v>122393589</v>
       </c>
       <c r="B24" t="n">
-        <v>90808</v>
+        <v>57395</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3298,26 +3174,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3325,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650587</v>
+        <v>650540</v>
       </c>
       <c r="R24" t="n">
-        <v>6671907</v>
+        <v>6671903</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3360,7 +3240,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,7 +3250,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393644</v>
+        <v>122393583</v>
       </c>
       <c r="B25" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,31 +3289,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3441,10 +3324,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650753</v>
+        <v>650841</v>
       </c>
       <c r="R25" t="n">
-        <v>6672196</v>
+        <v>6672286</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3476,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3486,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393649</v>
+        <v>122393654</v>
       </c>
       <c r="B26" t="n">
-        <v>100468</v>
+        <v>105317</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,38 +3412,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650513</v>
+        <v>650496</v>
       </c>
       <c r="R26" t="n">
-        <v>6671875</v>
+        <v>6671860</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3592,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3602,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,10 +3511,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393647</v>
+        <v>122393624</v>
       </c>
       <c r="B27" t="n">
-        <v>100468</v>
+        <v>91426</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3645,38 +3527,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>1339</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650531</v>
+        <v>650798</v>
       </c>
       <c r="R27" t="n">
-        <v>6671845</v>
+        <v>6672223</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3708,7 +3584,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3718,7 +3594,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3745,10 +3621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393622</v>
+        <v>122393651</v>
       </c>
       <c r="B28" t="n">
-        <v>91199</v>
+        <v>100477</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3757,25 +3633,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3783,10 +3660,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650619</v>
+        <v>650521</v>
       </c>
       <c r="R28" t="n">
-        <v>6671913</v>
+        <v>6671872</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3818,7 +3695,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3828,7 +3705,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,10 +3732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393611</v>
+        <v>122393642</v>
       </c>
       <c r="B29" t="n">
-        <v>90808</v>
+        <v>100477</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3867,41 +3744,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650587</v>
+        <v>650888</v>
       </c>
       <c r="R29" t="n">
-        <v>6671963</v>
+        <v>6672343</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3933,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3943,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3970,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393640</v>
+        <v>122393647</v>
       </c>
       <c r="B30" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3987,11 +3860,6 @@
       </c>
       <c r="E30" t="n">
         <v>222498</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4010,14 +3878,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650907</v>
+        <v>650531</v>
       </c>
       <c r="R30" t="n">
-        <v>6672335</v>
+        <v>6671845</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4049,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4059,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,10 +3954,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393636</v>
+        <v>122393650</v>
       </c>
       <c r="B31" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4103,11 +3971,6 @@
       </c>
       <c r="E31" t="n">
         <v>222498</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4126,14 +3989,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650878</v>
+        <v>650527</v>
       </c>
       <c r="R31" t="n">
-        <v>6672405</v>
+        <v>6671884</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4165,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4175,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4202,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122390399</v>
+        <v>122393585</v>
       </c>
       <c r="B32" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4214,20 +4077,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,21 +4100,25 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650718</v>
+        <v>650587</v>
       </c>
       <c r="R32" t="n">
-        <v>6672218</v>
+        <v>6671916</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4285,7 +4147,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4295,7 +4157,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4318,18 +4180,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393619</v>
+        <v>122393611</v>
       </c>
       <c r="B33" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4343,11 +4201,6 @@
       </c>
       <c r="E33" t="n">
         <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4369,10 +4222,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650561</v>
+        <v>650587</v>
       </c>
       <c r="R33" t="n">
-        <v>6671937</v>
+        <v>6671963</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4404,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4441,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393628</v>
+        <v>122393670</v>
       </c>
       <c r="B34" t="n">
-        <v>98202</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,50 +4306,36 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>3215</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650517</v>
+        <v>650673</v>
       </c>
       <c r="R34" t="n">
-        <v>6671888</v>
+        <v>6672256</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4528,7 +4367,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4538,7 +4377,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4565,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393637</v>
+        <v>122393633</v>
       </c>
       <c r="B35" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4582,11 +4421,6 @@
       </c>
       <c r="E35" t="n">
         <v>222498</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4605,14 +4439,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650982</v>
+        <v>650806</v>
       </c>
       <c r="R35" t="n">
-        <v>6672324</v>
+        <v>6672399</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4644,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4654,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393643</v>
+        <v>122393640</v>
       </c>
       <c r="B36" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4698,11 +4532,6 @@
       </c>
       <c r="E36" t="n">
         <v>222498</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4721,14 +4550,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650851</v>
+        <v>650907</v>
       </c>
       <c r="R36" t="n">
-        <v>6672282</v>
+        <v>6672335</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4760,7 +4589,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4770,7 +4599,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4797,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393599</v>
+        <v>122390399</v>
       </c>
       <c r="B37" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4809,20 +4638,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4837,11 +4661,7 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4849,13 +4669,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650684</v>
+        <v>650718</v>
       </c>
       <c r="R37" t="n">
-        <v>6672094</v>
+        <v>6672218</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4884,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4714,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4917,14 +4737,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393670</v>
+        <v>122393649</v>
       </c>
       <c r="B38" t="n">
-        <v>90575</v>
+        <v>100477</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4937,37 +4761,33 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650673</v>
+        <v>650513</v>
       </c>
       <c r="R38" t="n">
-        <v>6672256</v>
+        <v>6671875</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4819,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +4829,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +4856,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B39" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5052,26 +4872,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +4899,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R39" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +4944,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5177,11 +4997,6 @@
       </c>
       <c r="E40" t="n">
         <v>103015</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5284,10 +5099,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393604</v>
+        <v>122393587</v>
       </c>
       <c r="B41" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,26 +5115,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5332,13 +5142,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650559</v>
+        <v>650580</v>
       </c>
       <c r="R41" t="n">
-        <v>6671894</v>
+        <v>6671917</v>
       </c>
       <c r="S41" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5367,7 +5177,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5377,12 +5187,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393635</v>
+        <v>122393610</v>
       </c>
       <c r="B2" t="n">
-        <v>100477</v>
+        <v>90778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650861</v>
+        <v>650579</v>
       </c>
       <c r="R2" t="n">
-        <v>6672364</v>
+        <v>6671979</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -749,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393610</v>
+        <v>122393577</v>
       </c>
       <c r="B3" t="n">
-        <v>90778</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650579</v>
+        <v>650572</v>
       </c>
       <c r="R3" t="n">
-        <v>6671979</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -859,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393577</v>
+        <v>122393635</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>100477</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,38 +917,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650572</v>
+        <v>650861</v>
       </c>
       <c r="R4" t="n">
-        <v>6671983</v>
+        <v>6672364</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393623</v>
+        <v>122393669</v>
       </c>
       <c r="B9" t="n">
-        <v>91426</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,36 +1474,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650805</v>
+        <v>650502</v>
       </c>
       <c r="R9" t="n">
-        <v>6672392</v>
+        <v>6671865</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1535,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393617</v>
+        <v>122393623</v>
       </c>
       <c r="B10" t="n">
-        <v>90813</v>
+        <v>91426</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,20 +1593,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,14 +1615,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650568</v>
+        <v>650805</v>
       </c>
       <c r="R10" t="n">
-        <v>6671929</v>
+        <v>6672392</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1645,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393669</v>
+        <v>122393617</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,41 +1707,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650502</v>
+        <v>650568</v>
       </c>
       <c r="R11" t="n">
-        <v>6671865</v>
+        <v>6671929</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393598</v>
+        <v>122393578</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,15 +2145,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2161,16 +2161,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2180,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650520</v>
+        <v>650620</v>
       </c>
       <c r="R15" t="n">
-        <v>6671866</v>
+        <v>6671917</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2215,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393578</v>
+        <v>122393579</v>
       </c>
       <c r="B16" t="n">
         <v>5193</v>
@@ -2296,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650620</v>
+        <v>650568</v>
       </c>
       <c r="R16" t="n">
-        <v>6671917</v>
+        <v>6671816</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2331,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393579</v>
+        <v>122393628</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,31 +2377,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650568</v>
+        <v>650517</v>
       </c>
       <c r="R17" t="n">
-        <v>6671816</v>
+        <v>6671888</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393628</v>
+        <v>122393598</v>
       </c>
       <c r="B18" t="n">
-        <v>98211</v>
+        <v>57395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,34 +2496,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650517</v>
+        <v>650520</v>
       </c>
       <c r="R18" t="n">
-        <v>6671888</v>
+        <v>6671866</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393585</v>
+        <v>122393633</v>
       </c>
       <c r="B32" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,45 +4077,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650587</v>
+        <v>650806</v>
       </c>
       <c r="R32" t="n">
-        <v>6671916</v>
+        <v>6672399</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4147,7 +4139,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4157,7 +4149,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4184,10 +4176,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393611</v>
+        <v>122393585</v>
       </c>
       <c r="B33" t="n">
-        <v>90813</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,32 +4192,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>650587</v>
       </c>
       <c r="R33" t="n">
-        <v>6671963</v>
+        <v>6671916</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4257,7 +4258,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4268,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4295,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393670</v>
+        <v>122393611</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>90813</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4306,20 +4307,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4333,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650673</v>
+        <v>650587</v>
       </c>
       <c r="R34" t="n">
-        <v>6672256</v>
+        <v>6671963</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4367,7 +4368,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4377,7 +4378,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4405,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393633</v>
+        <v>122393670</v>
       </c>
       <c r="B35" t="n">
-        <v>100477</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,33 +4421,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650806</v>
+        <v>650673</v>
       </c>
       <c r="R35" t="n">
-        <v>6672399</v>
+        <v>6672256</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393669</v>
+        <v>122393623</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>91426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,45 +1474,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650502</v>
+        <v>650805</v>
       </c>
       <c r="R9" t="n">
-        <v>6671865</v>
+        <v>6672392</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1544,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393623</v>
+        <v>122393617</v>
       </c>
       <c r="B10" t="n">
-        <v>91426</v>
+        <v>90813</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,20 +1584,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,14 +1606,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650805</v>
+        <v>650568</v>
       </c>
       <c r="R10" t="n">
-        <v>6672392</v>
+        <v>6671929</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1654,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393617</v>
+        <v>122393669</v>
       </c>
       <c r="B11" t="n">
-        <v>90813</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,32 +1698,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650568</v>
+        <v>650502</v>
       </c>
       <c r="R11" t="n">
-        <v>6671929</v>
+        <v>6671865</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393583</v>
+        <v>122393654</v>
       </c>
       <c r="B25" t="n">
-        <v>57395</v>
+        <v>105317</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,45 +3289,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650841</v>
+        <v>650496</v>
       </c>
       <c r="R25" t="n">
-        <v>6672286</v>
+        <v>6671860</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3359,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393654</v>
+        <v>122393583</v>
       </c>
       <c r="B26" t="n">
-        <v>105317</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,41 +3404,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650496</v>
+        <v>650841</v>
       </c>
       <c r="R26" t="n">
-        <v>6671860</v>
+        <v>6672286</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393633</v>
+        <v>122393670</v>
       </c>
       <c r="B32" t="n">
-        <v>100477</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,33 +4081,32 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650806</v>
+        <v>650673</v>
       </c>
       <c r="R32" t="n">
-        <v>6672399</v>
+        <v>6672256</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4139,7 +4138,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4149,7 +4148,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393670</v>
+        <v>122393633</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>100477</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4421,32 +4420,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650673</v>
+        <v>650806</v>
       </c>
       <c r="R35" t="n">
-        <v>6672256</v>
+        <v>6672399</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393610</v>
+        <v>122393653</v>
       </c>
       <c r="B2" t="n">
-        <v>90778</v>
+        <v>100490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>222498</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650579</v>
+        <v>650726</v>
       </c>
       <c r="R2" t="n">
-        <v>6671979</v>
+        <v>6672208</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393577</v>
+        <v>122393636</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>100490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +807,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650572</v>
+        <v>650878</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6672405</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -864,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393635</v>
+        <v>122393599</v>
       </c>
       <c r="B4" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +919,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650861</v>
+        <v>650684</v>
       </c>
       <c r="R4" t="n">
-        <v>6672364</v>
+        <v>6672094</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -975,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393599</v>
+        <v>122393654</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>105330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,45 +1043,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650684</v>
+        <v>650496</v>
       </c>
       <c r="R5" t="n">
-        <v>6672094</v>
+        <v>6671860</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1094,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393614</v>
+        <v>122393589</v>
       </c>
       <c r="B6" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1167,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650587</v>
+        <v>650540</v>
       </c>
       <c r="R6" t="n">
-        <v>6671907</v>
+        <v>6671903</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1204,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393632</v>
+        <v>122393585</v>
       </c>
       <c r="B7" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,37 +1287,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650791</v>
+        <v>650587</v>
       </c>
       <c r="R7" t="n">
-        <v>6672382</v>
+        <v>6671916</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1315,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393619</v>
+        <v>122393640</v>
       </c>
       <c r="B8" t="n">
-        <v>90813</v>
+        <v>100490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,36 +1411,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650561</v>
+        <v>650907</v>
       </c>
       <c r="R8" t="n">
-        <v>6671937</v>
+        <v>6672335</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1425,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1488,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393623</v>
+        <v>122393577</v>
       </c>
       <c r="B9" t="n">
-        <v>91426</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,32 +1531,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650805</v>
+        <v>650572</v>
       </c>
       <c r="R9" t="n">
-        <v>6672392</v>
+        <v>6671983</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1535,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393617</v>
+        <v>122393643</v>
       </c>
       <c r="B10" t="n">
-        <v>90813</v>
+        <v>100490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,25 +1648,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650568</v>
+        <v>650851</v>
       </c>
       <c r="R10" t="n">
-        <v>6671929</v>
+        <v>6672282</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1645,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393669</v>
+        <v>122393628</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,45 +1764,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650502</v>
+        <v>650517</v>
       </c>
       <c r="R11" t="n">
-        <v>6671865</v>
+        <v>6671888</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1764,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1849,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393634</v>
+        <v>122393642</v>
       </c>
       <c r="B12" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,6 +1893,11 @@
       </c>
       <c r="E12" t="n">
         <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1836,14 +1916,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650818</v>
+        <v>650888</v>
       </c>
       <c r="R12" t="n">
-        <v>6672400</v>
+        <v>6672343</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1875,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393637</v>
+        <v>122393610</v>
       </c>
       <c r="B13" t="n">
-        <v>100477</v>
+        <v>90791</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,33 +2008,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650982</v>
+        <v>650579</v>
       </c>
       <c r="R13" t="n">
-        <v>6672324</v>
+        <v>6671979</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1986,7 +2070,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +2080,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +2110,7 @@
         <v>122393622</v>
       </c>
       <c r="B14" t="n">
-        <v>91204</v>
+        <v>91217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2133,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393578</v>
+        <v>122393598</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,15 +2229,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2161,13 +2250,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2177,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650620</v>
+        <v>650520</v>
       </c>
       <c r="R15" t="n">
-        <v>6671917</v>
+        <v>6671866</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2212,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2314,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393579</v>
+        <v>122393635</v>
       </c>
       <c r="B16" t="n">
-        <v>5193</v>
+        <v>100490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,38 +2357,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650568</v>
+        <v>650861</v>
       </c>
       <c r="R16" t="n">
-        <v>6671816</v>
+        <v>6672364</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2328,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393628</v>
+        <v>122390399</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>57753</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,48 +2469,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650517</v>
+        <v>650718</v>
       </c>
       <c r="R17" t="n">
-        <v>6671888</v>
+        <v>6672218</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2550,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,14 +2573,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393598</v>
+        <v>122393633</v>
       </c>
       <c r="B18" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,45 +2593,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650520</v>
+        <v>650806</v>
       </c>
       <c r="R18" t="n">
-        <v>6671866</v>
+        <v>6672399</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2566,7 +2660,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2670,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393646</v>
+        <v>122393670</v>
       </c>
       <c r="B19" t="n">
-        <v>100477</v>
+        <v>90593</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,33 +2713,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>3215</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650560</v>
+        <v>650673</v>
       </c>
       <c r="R19" t="n">
-        <v>6671817</v>
+        <v>6672256</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2677,7 +2775,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2687,7 +2785,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393643</v>
+        <v>122393624</v>
       </c>
       <c r="B20" t="n">
-        <v>100477</v>
+        <v>91439</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,22 +2828,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1339</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2753,10 +2855,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650851</v>
+        <v>650798</v>
       </c>
       <c r="R20" t="n">
-        <v>6672282</v>
+        <v>6672223</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2788,7 +2890,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2900,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2927,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393653</v>
+        <v>122393650</v>
       </c>
       <c r="B21" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,6 +2944,11 @@
       </c>
       <c r="E21" t="n">
         <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2860,14 +2967,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650726</v>
+        <v>650527</v>
       </c>
       <c r="R21" t="n">
-        <v>6672208</v>
+        <v>6671884</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2899,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +3016,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,10 +3043,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393644</v>
+        <v>122393617</v>
       </c>
       <c r="B22" t="n">
-        <v>100477</v>
+        <v>90826</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,26 +3055,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2975,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650753</v>
+        <v>650568</v>
       </c>
       <c r="R22" t="n">
-        <v>6672196</v>
+        <v>6671929</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3010,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393636</v>
+        <v>122393646</v>
       </c>
       <c r="B23" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,6 +3175,11 @@
       </c>
       <c r="E23" t="n">
         <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3082,14 +3198,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650878</v>
+        <v>650560</v>
       </c>
       <c r="R23" t="n">
-        <v>6672405</v>
+        <v>6671817</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3121,7 +3237,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3247,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3274,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393589</v>
+        <v>122393632</v>
       </c>
       <c r="B24" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,45 +3286,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650540</v>
+        <v>650791</v>
       </c>
       <c r="R24" t="n">
-        <v>6671903</v>
+        <v>6672382</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3240,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3250,7 +3363,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393654</v>
+        <v>122393619</v>
       </c>
       <c r="B25" t="n">
-        <v>105317</v>
+        <v>90826</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,41 +3402,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650496</v>
+        <v>650561</v>
       </c>
       <c r="R25" t="n">
-        <v>6671860</v>
+        <v>6671937</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3355,7 +3468,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3478,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3505,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393583</v>
+        <v>122393614</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,41 +3521,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650841</v>
+        <v>650587</v>
       </c>
       <c r="R26" t="n">
-        <v>6672286</v>
+        <v>6671907</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3474,7 +3583,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3484,7 +3593,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,10 +3620,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393624</v>
+        <v>122393623</v>
       </c>
       <c r="B27" t="n">
-        <v>91426</v>
+        <v>91439</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3528,6 +3637,11 @@
       </c>
       <c r="E27" t="n">
         <v>1339</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3545,14 +3659,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650798</v>
+        <v>650805</v>
       </c>
       <c r="R27" t="n">
-        <v>6672223</v>
+        <v>6672392</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3584,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3594,7 +3708,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,10 +3735,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393651</v>
+        <v>122393579</v>
       </c>
       <c r="B28" t="n">
-        <v>100477</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3637,22 +3751,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3660,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650521</v>
+        <v>650568</v>
       </c>
       <c r="R28" t="n">
-        <v>6671872</v>
+        <v>6671816</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3695,7 +3819,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,7 +3829,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,10 +3856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393642</v>
+        <v>122393634</v>
       </c>
       <c r="B29" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3749,6 +3873,11 @@
       </c>
       <c r="E29" t="n">
         <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3767,14 +3896,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650888</v>
+        <v>650818</v>
       </c>
       <c r="R29" t="n">
-        <v>6672343</v>
+        <v>6672400</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3806,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3945,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393647</v>
+        <v>122393644</v>
       </c>
       <c r="B30" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3860,6 +3989,11 @@
       </c>
       <c r="E30" t="n">
         <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3878,14 +4012,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650531</v>
+        <v>650753</v>
       </c>
       <c r="R30" t="n">
-        <v>6671845</v>
+        <v>6672196</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3917,7 +4051,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3927,7 +4061,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3954,10 +4088,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393650</v>
+        <v>122393611</v>
       </c>
       <c r="B31" t="n">
-        <v>100477</v>
+        <v>90826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,37 +4100,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650527</v>
+        <v>650587</v>
       </c>
       <c r="R31" t="n">
-        <v>6671884</v>
+        <v>6671963</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4028,7 +4166,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4176,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4203,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393670</v>
+        <v>122393647</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>100490</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,32 +4219,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3215</v>
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650673</v>
+        <v>650531</v>
       </c>
       <c r="R32" t="n">
-        <v>6672256</v>
+        <v>6671845</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4138,7 +4282,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4148,7 +4292,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,10 +4319,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393585</v>
+        <v>122393651</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4187,34 +4331,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4222,10 +4363,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650587</v>
+        <v>650521</v>
       </c>
       <c r="R33" t="n">
-        <v>6671916</v>
+        <v>6671872</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4257,7 +4398,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4408,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4435,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393611</v>
+        <v>122393583</v>
       </c>
       <c r="B34" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,21 +4451,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4332,10 +4487,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650587</v>
+        <v>650841</v>
       </c>
       <c r="R34" t="n">
-        <v>6671963</v>
+        <v>6672286</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4367,7 +4522,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4377,7 +4532,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4559,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393633</v>
+        <v>122393578</v>
       </c>
       <c r="B35" t="n">
-        <v>100477</v>
+        <v>5193</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,33 +4575,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>105930</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650806</v>
+        <v>650620</v>
       </c>
       <c r="R35" t="n">
-        <v>6672399</v>
+        <v>6671917</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4478,7 +4643,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4653,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393640</v>
+        <v>122393649</v>
       </c>
       <c r="B36" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,6 +4697,11 @@
       </c>
       <c r="E36" t="n">
         <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4550,14 +4720,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650907</v>
+        <v>650513</v>
       </c>
       <c r="R36" t="n">
-        <v>6672335</v>
+        <v>6671875</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4589,7 +4759,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4599,7 +4769,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4626,10 +4796,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122390399</v>
+        <v>122393669</v>
       </c>
       <c r="B37" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,15 +4808,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4661,21 +4836,25 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650718</v>
+        <v>650502</v>
       </c>
       <c r="R37" t="n">
-        <v>6672218</v>
+        <v>6671865</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4704,7 +4883,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,7 +4893,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4737,18 +4916,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393649</v>
+        <v>122393637</v>
       </c>
       <c r="B38" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4762,6 +4937,11 @@
       </c>
       <c r="E38" t="n">
         <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4780,14 +4960,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650513</v>
+        <v>650982</v>
       </c>
       <c r="R38" t="n">
-        <v>6671875</v>
+        <v>6672324</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4819,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4829,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4856,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393604</v>
+        <v>122393587</v>
       </c>
       <c r="B39" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4872,21 +5052,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4899,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650559</v>
+        <v>650580</v>
       </c>
       <c r="R39" t="n">
-        <v>6671894</v>
+        <v>6671917</v>
       </c>
       <c r="S39" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4934,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,12 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393604</v>
       </c>
       <c r="B40" t="n">
-        <v>57749</v>
+        <v>57536</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,25 +5172,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5023,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650559</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6671894</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5058,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5253,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5099,10 +5289,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393587</v>
+        <v>122393605</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>57753</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5111,15 +5301,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103015</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5142,13 +5337,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650580</v>
+        <v>650566</v>
       </c>
       <c r="R41" t="n">
-        <v>6671917</v>
+        <v>6671827</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5177,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5187,7 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393653</v>
+        <v>122393623</v>
       </c>
       <c r="B2" t="n">
-        <v>100490</v>
+        <v>91452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650726</v>
+        <v>650805</v>
       </c>
       <c r="R2" t="n">
-        <v>6672208</v>
+        <v>6672392</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393636</v>
+        <v>122393670</v>
       </c>
       <c r="B3" t="n">
-        <v>100490</v>
+        <v>90606</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650878</v>
+        <v>650673</v>
       </c>
       <c r="R3" t="n">
-        <v>6672405</v>
+        <v>6672256</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393599</v>
+        <v>122393611</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +921,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650684</v>
+        <v>650587</v>
       </c>
       <c r="R4" t="n">
-        <v>6672094</v>
+        <v>6671963</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393654</v>
+        <v>122393653</v>
       </c>
       <c r="B5" t="n">
-        <v>105330</v>
+        <v>100503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,42 +1036,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650496</v>
+        <v>650726</v>
       </c>
       <c r="R5" t="n">
-        <v>6671860</v>
+        <v>6672208</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393589</v>
+        <v>122393643</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,50 +1148,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650540</v>
+        <v>650851</v>
       </c>
       <c r="R6" t="n">
-        <v>6671903</v>
+        <v>6672282</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393585</v>
+        <v>122393636</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,50 +1264,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650587</v>
+        <v>650878</v>
       </c>
       <c r="R7" t="n">
-        <v>6671916</v>
+        <v>6672405</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1362,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393640</v>
+        <v>122393610</v>
       </c>
       <c r="B8" t="n">
-        <v>100490</v>
+        <v>90804</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,38 +1384,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650907</v>
+        <v>650579</v>
       </c>
       <c r="R8" t="n">
-        <v>6672335</v>
+        <v>6671979</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1478,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393577</v>
+        <v>122393635</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>100503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,43 +1499,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650572</v>
+        <v>650861</v>
       </c>
       <c r="R9" t="n">
-        <v>6671983</v>
+        <v>6672364</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1599,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393643</v>
+        <v>122393579</v>
       </c>
       <c r="B10" t="n">
-        <v>100490</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,38 +1615,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650851</v>
+        <v>650568</v>
       </c>
       <c r="R10" t="n">
-        <v>6672282</v>
+        <v>6671816</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393628</v>
+        <v>122393649</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,37 +1732,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1804,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650517</v>
+        <v>650513</v>
       </c>
       <c r="R11" t="n">
-        <v>6671888</v>
+        <v>6671875</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1839,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393642</v>
+        <v>122393646</v>
       </c>
       <c r="B12" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,14 +1876,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650888</v>
+        <v>650560</v>
       </c>
       <c r="R12" t="n">
-        <v>6672343</v>
+        <v>6671817</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1955,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393610</v>
+        <v>122393654</v>
       </c>
       <c r="B13" t="n">
-        <v>90791</v>
+        <v>105343</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,37 +1968,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650579</v>
+        <v>650496</v>
       </c>
       <c r="R13" t="n">
-        <v>6671979</v>
+        <v>6671860</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2070,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2080,7 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393622</v>
+        <v>122393640</v>
       </c>
       <c r="B14" t="n">
-        <v>91217</v>
+        <v>100503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,36 +2084,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650619</v>
+        <v>650907</v>
       </c>
       <c r="R14" t="n">
-        <v>6671913</v>
+        <v>6672335</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2180,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393598</v>
+        <v>122393637</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,50 +2200,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650520</v>
+        <v>650982</v>
       </c>
       <c r="R15" t="n">
-        <v>6671866</v>
+        <v>6672324</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2304,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393635</v>
+        <v>122393644</v>
       </c>
       <c r="B16" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2381,14 +2344,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650861</v>
+        <v>650753</v>
       </c>
       <c r="R16" t="n">
-        <v>6672364</v>
+        <v>6672196</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2420,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122390399</v>
+        <v>122393650</v>
       </c>
       <c r="B17" t="n">
-        <v>57753</v>
+        <v>100503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,45 +2436,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650718</v>
+        <v>650527</v>
       </c>
       <c r="R17" t="n">
-        <v>6672218</v>
+        <v>6671884</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,18 +2532,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393633</v>
+        <v>122390399</v>
       </c>
       <c r="B18" t="n">
-        <v>100490</v>
+        <v>57753</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,41 +2552,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650806</v>
+        <v>650718</v>
       </c>
       <c r="R18" t="n">
-        <v>6672399</v>
+        <v>6672218</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2660,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2670,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,14 +2652,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393670</v>
+        <v>122393628</v>
       </c>
       <c r="B19" t="n">
-        <v>90593</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,41 +2672,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650673</v>
+        <v>650517</v>
       </c>
       <c r="R19" t="n">
-        <v>6672256</v>
+        <v>6671888</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2775,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2785,7 +2757,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393624</v>
+        <v>122393633</v>
       </c>
       <c r="B20" t="n">
-        <v>91439</v>
+        <v>100503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,37 +2800,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650798</v>
+        <v>650806</v>
       </c>
       <c r="R20" t="n">
-        <v>6672223</v>
+        <v>6672399</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2890,7 +2863,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,7 +2873,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393650</v>
+        <v>122393642</v>
       </c>
       <c r="B21" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,14 +2940,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650527</v>
+        <v>650888</v>
       </c>
       <c r="R21" t="n">
-        <v>6671884</v>
+        <v>6672343</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3006,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,7 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393617</v>
+        <v>122393622</v>
       </c>
       <c r="B22" t="n">
-        <v>90826</v>
+        <v>91230</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3059,21 +3032,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3082,14 +3050,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650568</v>
+        <v>650619</v>
       </c>
       <c r="R22" t="n">
-        <v>6671929</v>
+        <v>6671913</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3121,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393646</v>
+        <v>122393599</v>
       </c>
       <c r="B23" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,42 +3138,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650560</v>
+        <v>650684</v>
       </c>
       <c r="R23" t="n">
-        <v>6671817</v>
+        <v>6672094</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3237,7 +3213,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3247,7 +3223,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,10 +3250,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393632</v>
+        <v>122393619</v>
       </c>
       <c r="B24" t="n">
-        <v>100490</v>
+        <v>90839</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3286,42 +3262,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650791</v>
+        <v>650561</v>
       </c>
       <c r="R24" t="n">
-        <v>6672382</v>
+        <v>6671937</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3353,7 +3328,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3363,7 +3338,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393619</v>
+        <v>122393632</v>
       </c>
       <c r="B25" t="n">
-        <v>90826</v>
+        <v>100503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3402,41 +3377,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650561</v>
+        <v>650791</v>
       </c>
       <c r="R25" t="n">
-        <v>6671937</v>
+        <v>6672382</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3468,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3478,7 +3454,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,10 +3481,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393614</v>
+        <v>122393585</v>
       </c>
       <c r="B26" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3521,26 +3497,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3551,7 +3536,7 @@
         <v>650587</v>
       </c>
       <c r="R26" t="n">
-        <v>6671907</v>
+        <v>6671916</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3583,7 +3568,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3593,7 +3578,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393623</v>
+        <v>122393583</v>
       </c>
       <c r="B27" t="n">
-        <v>91439</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3632,41 +3617,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650805</v>
+        <v>650841</v>
       </c>
       <c r="R27" t="n">
-        <v>6672392</v>
+        <v>6672286</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3698,7 +3692,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3708,7 +3702,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3735,7 +3729,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393579</v>
+        <v>122393578</v>
       </c>
       <c r="B28" t="n">
         <v>5193</v>
@@ -3784,10 +3778,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650568</v>
+        <v>650620</v>
       </c>
       <c r="R28" t="n">
-        <v>6671816</v>
+        <v>6671917</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3819,7 +3813,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3829,7 +3823,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393634</v>
+        <v>122393589</v>
       </c>
       <c r="B29" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3868,42 +3862,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650818</v>
+        <v>650540</v>
       </c>
       <c r="R29" t="n">
-        <v>6672400</v>
+        <v>6671903</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3935,7 +3937,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3947,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393644</v>
+        <v>122393651</v>
       </c>
       <c r="B30" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4012,14 +4014,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650753</v>
+        <v>650521</v>
       </c>
       <c r="R30" t="n">
-        <v>6672196</v>
+        <v>6671872</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4051,7 +4053,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4061,7 +4063,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4088,10 +4090,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393611</v>
+        <v>122393634</v>
       </c>
       <c r="B31" t="n">
-        <v>90826</v>
+        <v>100503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4100,41 +4102,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650587</v>
+        <v>650818</v>
       </c>
       <c r="R31" t="n">
-        <v>6671963</v>
+        <v>6672400</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4166,7 +4169,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4176,7 +4179,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4203,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393647</v>
+        <v>122393617</v>
       </c>
       <c r="B32" t="n">
-        <v>100490</v>
+        <v>90839</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4215,42 +4218,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650531</v>
+        <v>650568</v>
       </c>
       <c r="R32" t="n">
-        <v>6671845</v>
+        <v>6671929</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4282,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4292,7 +4294,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4319,10 +4321,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393651</v>
+        <v>122393647</v>
       </c>
       <c r="B33" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4363,10 +4365,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650521</v>
+        <v>650531</v>
       </c>
       <c r="R33" t="n">
-        <v>6671872</v>
+        <v>6671845</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4398,7 +4400,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4408,7 +4410,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4435,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393583</v>
+        <v>122393614</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4451,46 +4453,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650841</v>
+        <v>650587</v>
       </c>
       <c r="R34" t="n">
-        <v>6672286</v>
+        <v>6671907</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4522,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4532,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4559,10 +4552,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393578</v>
+        <v>122393624</v>
       </c>
       <c r="B35" t="n">
-        <v>5193</v>
+        <v>91452</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4575,43 +4568,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650620</v>
+        <v>650798</v>
       </c>
       <c r="R35" t="n">
-        <v>6671917</v>
+        <v>6672223</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4643,7 +4630,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4653,7 +4640,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4667,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393649</v>
+        <v>122393669</v>
       </c>
       <c r="B36" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,42 +4679,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650513</v>
+        <v>650502</v>
       </c>
       <c r="R36" t="n">
-        <v>6671875</v>
+        <v>6671865</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4759,7 +4754,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4769,7 +4764,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4796,10 +4791,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393669</v>
+        <v>122393577</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4808,50 +4803,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650502</v>
+        <v>650572</v>
       </c>
       <c r="R37" t="n">
-        <v>6671865</v>
+        <v>6671983</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4883,7 +4875,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4893,7 +4885,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4920,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393637</v>
+        <v>122393598</v>
       </c>
       <c r="B38" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4932,42 +4924,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650982</v>
+        <v>650520</v>
       </c>
       <c r="R38" t="n">
-        <v>6672324</v>
+        <v>6671866</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393587</v>
+        <v>122393605</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,20 +5048,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650580</v>
+        <v>650566</v>
       </c>
       <c r="R39" t="n">
-        <v>6671917</v>
+        <v>6671827</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B41" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5301,20 +5301,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R41" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S41" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -2660,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393628</v>
+        <v>122393633</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2672,50 +2672,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650517</v>
+        <v>650806</v>
       </c>
       <c r="R19" t="n">
-        <v>6671888</v>
+        <v>6672399</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2747,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2757,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,10 +2776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393633</v>
+        <v>122393628</v>
       </c>
       <c r="B20" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,42 +2788,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650806</v>
+        <v>650517</v>
       </c>
       <c r="R20" t="n">
-        <v>6672399</v>
+        <v>6671888</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4321,10 +4321,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393647</v>
+        <v>122393614</v>
       </c>
       <c r="B33" t="n">
-        <v>100503</v>
+        <v>90839</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4333,31 +4333,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4365,10 +4364,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650531</v>
+        <v>650587</v>
       </c>
       <c r="R33" t="n">
-        <v>6671845</v>
+        <v>6671907</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4400,7 +4399,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4410,7 +4409,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4437,10 +4436,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393614</v>
+        <v>122393647</v>
       </c>
       <c r="B34" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4449,30 +4448,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650587</v>
+        <v>650531</v>
       </c>
       <c r="R34" t="n">
-        <v>6671907</v>
+        <v>6671845</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393623</v>
+        <v>122393624</v>
       </c>
       <c r="B2" t="n">
         <v>91452</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650805</v>
+        <v>650798</v>
       </c>
       <c r="R2" t="n">
-        <v>6672392</v>
+        <v>6672223</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393670</v>
+        <v>122393623</v>
       </c>
       <c r="B3" t="n">
-        <v>90606</v>
+        <v>91452</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650673</v>
+        <v>650805</v>
       </c>
       <c r="R3" t="n">
-        <v>6672256</v>
+        <v>6672392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393611</v>
+        <v>122393579</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,41 +917,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650587</v>
+        <v>650568</v>
       </c>
       <c r="R4" t="n">
-        <v>6671963</v>
+        <v>6671816</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393653</v>
+        <v>122393642</v>
       </c>
       <c r="B5" t="n">
         <v>100503</v>
@@ -1060,14 +1066,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650726</v>
+        <v>650888</v>
       </c>
       <c r="R5" t="n">
-        <v>6672208</v>
+        <v>6672343</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393643</v>
+        <v>122393651</v>
       </c>
       <c r="B6" t="n">
         <v>100503</v>
@@ -1176,14 +1182,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650851</v>
+        <v>650521</v>
       </c>
       <c r="R6" t="n">
-        <v>6672282</v>
+        <v>6671872</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1215,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393636</v>
+        <v>122393640</v>
       </c>
       <c r="B7" t="n">
         <v>100503</v>
@@ -1292,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650878</v>
+        <v>650907</v>
       </c>
       <c r="R7" t="n">
-        <v>6672405</v>
+        <v>6672335</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393610</v>
+        <v>122393654</v>
       </c>
       <c r="B8" t="n">
-        <v>90804</v>
+        <v>105343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,37 +1390,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650579</v>
+        <v>650496</v>
       </c>
       <c r="R8" t="n">
-        <v>6671979</v>
+        <v>6671860</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1446,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393635</v>
+        <v>122393650</v>
       </c>
       <c r="B9" t="n">
         <v>100503</v>
@@ -1523,14 +1534,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650861</v>
+        <v>650527</v>
       </c>
       <c r="R9" t="n">
-        <v>6672364</v>
+        <v>6671884</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1562,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393579</v>
+        <v>122393647</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>100503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,32 +1626,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650568</v>
+        <v>650531</v>
       </c>
       <c r="R10" t="n">
-        <v>6671816</v>
+        <v>6671845</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1683,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393649</v>
+        <v>122393611</v>
       </c>
       <c r="B11" t="n">
-        <v>100503</v>
+        <v>90839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,42 +1738,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650513</v>
+        <v>650587</v>
       </c>
       <c r="R11" t="n">
-        <v>6671875</v>
+        <v>6671963</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1799,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,7 +1841,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393646</v>
+        <v>122393634</v>
       </c>
       <c r="B12" t="n">
         <v>100503</v>
@@ -1876,14 +1881,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650560</v>
+        <v>650818</v>
       </c>
       <c r="R12" t="n">
-        <v>6671817</v>
+        <v>6672400</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393654</v>
+        <v>122393617</v>
       </c>
       <c r="B13" t="n">
-        <v>105343</v>
+        <v>90839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,46 +1969,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650496</v>
+        <v>650568</v>
       </c>
       <c r="R13" t="n">
-        <v>6671860</v>
+        <v>6671929</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393640</v>
+        <v>122393646</v>
       </c>
       <c r="B14" t="n">
         <v>100503</v>
@@ -2112,14 +2112,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650907</v>
+        <v>650560</v>
       </c>
       <c r="R14" t="n">
-        <v>6672335</v>
+        <v>6671817</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393637</v>
+        <v>122393598</v>
       </c>
       <c r="B15" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,42 +2200,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650982</v>
+        <v>650520</v>
       </c>
       <c r="R15" t="n">
-        <v>6672324</v>
+        <v>6671866</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2267,7 +2275,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2285,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393644</v>
+        <v>122393599</v>
       </c>
       <c r="B16" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,31 +2324,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2348,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650753</v>
+        <v>650684</v>
       </c>
       <c r="R16" t="n">
-        <v>6672196</v>
+        <v>6672094</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2383,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2409,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393650</v>
+        <v>122390399</v>
       </c>
       <c r="B17" t="n">
-        <v>100503</v>
+        <v>57753</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,41 +2452,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650527</v>
+        <v>650718</v>
       </c>
       <c r="R17" t="n">
-        <v>6671884</v>
+        <v>6672218</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2529,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,14 +2552,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122390399</v>
+        <v>122393628</v>
       </c>
       <c r="B18" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2548,49 +2572,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650718</v>
+        <v>650517</v>
       </c>
       <c r="R18" t="n">
-        <v>6672218</v>
+        <v>6671888</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2619,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2657,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,15 +2680,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393633</v>
+        <v>122393635</v>
       </c>
       <c r="B19" t="n">
         <v>100503</v>
@@ -2704,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650806</v>
+        <v>650861</v>
       </c>
       <c r="R19" t="n">
-        <v>6672399</v>
+        <v>6672364</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2739,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,10 +2800,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393628</v>
+        <v>122393636</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,50 +2812,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650517</v>
+        <v>650878</v>
       </c>
       <c r="R20" t="n">
-        <v>6671888</v>
+        <v>6672405</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2863,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2873,7 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,7 +2916,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393642</v>
+        <v>122393644</v>
       </c>
       <c r="B21" t="n">
         <v>100503</v>
@@ -2940,14 +2956,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650888</v>
+        <v>650753</v>
       </c>
       <c r="R21" t="n">
-        <v>6672343</v>
+        <v>6672196</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2979,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,7 +3005,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393622</v>
+        <v>122393577</v>
       </c>
       <c r="B22" t="n">
-        <v>91230</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,36 +3044,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650619</v>
+        <v>650572</v>
       </c>
       <c r="R22" t="n">
-        <v>6671913</v>
+        <v>6671983</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3089,7 +3116,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3126,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3153,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393599</v>
+        <v>122393653</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,39 +3165,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3178,10 +3197,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650684</v>
+        <v>650726</v>
       </c>
       <c r="R23" t="n">
-        <v>6672094</v>
+        <v>6672208</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3213,7 +3232,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3223,7 +3242,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3250,10 +3269,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393619</v>
+        <v>122393649</v>
       </c>
       <c r="B24" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3262,41 +3281,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650561</v>
+        <v>650513</v>
       </c>
       <c r="R24" t="n">
-        <v>6671937</v>
+        <v>6671875</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3328,7 +3348,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3338,7 +3358,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393632</v>
+        <v>122393610</v>
       </c>
       <c r="B25" t="n">
-        <v>100503</v>
+        <v>90804</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3381,38 +3401,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650791</v>
+        <v>650579</v>
       </c>
       <c r="R25" t="n">
-        <v>6672382</v>
+        <v>6671979</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3444,7 +3463,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,7 +3473,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3605,10 +3624,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393583</v>
+        <v>122393633</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3617,50 +3636,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650841</v>
+        <v>650806</v>
       </c>
       <c r="R27" t="n">
-        <v>6672286</v>
+        <v>6672399</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3692,7 +3703,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3702,7 +3713,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3729,10 +3740,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393578</v>
+        <v>122393619</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>90839</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3741,47 +3752,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650620</v>
+        <v>650561</v>
       </c>
       <c r="R28" t="n">
-        <v>6671917</v>
+        <v>6671937</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3813,7 +3818,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3823,7 +3828,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3850,7 +3855,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393589</v>
+        <v>122393669</v>
       </c>
       <c r="B29" t="n">
         <v>57399</v>
@@ -3892,20 +3897,20 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650540</v>
+        <v>650502</v>
       </c>
       <c r="R29" t="n">
-        <v>6671903</v>
+        <v>6671865</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3937,7 +3942,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3947,7 +3952,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3974,7 +3979,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393651</v>
+        <v>122393643</v>
       </c>
       <c r="B30" t="n">
         <v>100503</v>
@@ -4014,14 +4019,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650521</v>
+        <v>650851</v>
       </c>
       <c r="R30" t="n">
-        <v>6671872</v>
+        <v>6672282</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4053,7 +4058,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4063,7 +4068,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,10 +4095,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393634</v>
+        <v>122393589</v>
       </c>
       <c r="B31" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4102,42 +4107,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650818</v>
+        <v>650540</v>
       </c>
       <c r="R31" t="n">
-        <v>6672400</v>
+        <v>6671903</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4169,7 +4182,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4179,7 +4192,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4206,7 +4219,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393617</v>
+        <v>122393614</v>
       </c>
       <c r="B32" t="n">
         <v>90839</v>
@@ -4245,14 +4258,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650568</v>
+        <v>650587</v>
       </c>
       <c r="R32" t="n">
-        <v>6671929</v>
+        <v>6671907</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4284,7 +4297,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,7 +4307,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4321,10 +4334,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393614</v>
+        <v>122393622</v>
       </c>
       <c r="B33" t="n">
-        <v>90839</v>
+        <v>91230</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4337,21 +4350,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4364,10 +4372,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650587</v>
+        <v>650619</v>
       </c>
       <c r="R33" t="n">
-        <v>6671907</v>
+        <v>6671913</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4399,7 +4407,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4409,7 +4417,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4436,7 +4444,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393647</v>
+        <v>122393632</v>
       </c>
       <c r="B34" t="n">
         <v>100503</v>
@@ -4476,14 +4484,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650531</v>
+        <v>650791</v>
       </c>
       <c r="R34" t="n">
-        <v>6671845</v>
+        <v>6672382</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4515,7 +4523,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4533,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,10 +4560,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393624</v>
+        <v>122393670</v>
       </c>
       <c r="B35" t="n">
-        <v>91452</v>
+        <v>90605</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4568,21 +4576,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4595,10 +4603,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650798</v>
+        <v>650673</v>
       </c>
       <c r="R35" t="n">
-        <v>6672223</v>
+        <v>6672256</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4630,7 +4638,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4640,7 +4648,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4667,10 +4675,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393669</v>
+        <v>122393578</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4679,20 +4687,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4700,29 +4708,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650502</v>
+        <v>650620</v>
       </c>
       <c r="R36" t="n">
-        <v>6671865</v>
+        <v>6671917</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4754,7 +4759,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4764,7 +4769,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4791,10 +4796,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393577</v>
+        <v>122393583</v>
       </c>
       <c r="B37" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4803,34 +4808,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4840,10 +4848,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650572</v>
+        <v>650841</v>
       </c>
       <c r="R37" t="n">
-        <v>6671983</v>
+        <v>6672286</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4875,7 +4883,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4885,7 +4893,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4912,10 +4920,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393598</v>
+        <v>122393637</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,50 +4932,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650520</v>
+        <v>650982</v>
       </c>
       <c r="R38" t="n">
-        <v>6671866</v>
+        <v>6672324</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393605</v>
+        <v>122393604</v>
       </c>
       <c r="B39" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,30 +5048,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650566</v>
+        <v>650559</v>
       </c>
       <c r="R39" t="n">
-        <v>6671827</v>
+        <v>6671894</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5165,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B40" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,30 +5177,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5208,13 +5213,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R40" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,12 +5258,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393611</v>
+        <v>122393634</v>
       </c>
       <c r="B11" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,41 +1738,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650587</v>
+        <v>650818</v>
       </c>
       <c r="R11" t="n">
-        <v>6671963</v>
+        <v>6672400</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1804,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393634</v>
+        <v>122393611</v>
       </c>
       <c r="B12" t="n">
-        <v>100503</v>
+        <v>90839</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,42 +1854,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650818</v>
+        <v>650587</v>
       </c>
       <c r="R12" t="n">
-        <v>6672400</v>
+        <v>6671963</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393617</v>
+        <v>122393646</v>
       </c>
       <c r="B13" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,41 +1969,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650568</v>
+        <v>650560</v>
       </c>
       <c r="R13" t="n">
-        <v>6671929</v>
+        <v>6671817</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2035,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2045,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393646</v>
+        <v>122393617</v>
       </c>
       <c r="B14" t="n">
-        <v>100503</v>
+        <v>90839</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,42 +2085,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650560</v>
+        <v>650568</v>
       </c>
       <c r="R14" t="n">
-        <v>6671817</v>
+        <v>6671929</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393643</v>
+        <v>122393589</v>
       </c>
       <c r="B30" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3991,42 +3991,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650851</v>
+        <v>650540</v>
       </c>
       <c r="R30" t="n">
-        <v>6672282</v>
+        <v>6671903</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4058,7 +4066,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4068,7 +4076,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4095,10 +4103,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393589</v>
+        <v>122393643</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4107,50 +4115,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650540</v>
+        <v>650851</v>
       </c>
       <c r="R31" t="n">
-        <v>6671903</v>
+        <v>6672282</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4560,10 +4560,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393670</v>
+        <v>122393578</v>
       </c>
       <c r="B35" t="n">
-        <v>90605</v>
+        <v>5193</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4576,37 +4576,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650673</v>
+        <v>650620</v>
       </c>
       <c r="R35" t="n">
-        <v>6672256</v>
+        <v>6671917</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4638,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4648,7 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4675,10 +4681,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393578</v>
+        <v>122393670</v>
       </c>
       <c r="B36" t="n">
-        <v>5193</v>
+        <v>90605</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4691,43 +4697,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650620</v>
+        <v>650673</v>
       </c>
       <c r="R36" t="n">
-        <v>6671917</v>
+        <v>6672256</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393583</v>
+        <v>122393637</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4808,50 +4808,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650841</v>
+        <v>650982</v>
       </c>
       <c r="R37" t="n">
-        <v>6672286</v>
+        <v>6672324</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4883,7 +4875,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4893,7 +4885,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4920,10 +4912,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393637</v>
+        <v>122393583</v>
       </c>
       <c r="B38" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4932,42 +4924,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650982</v>
+        <v>650841</v>
       </c>
       <c r="R38" t="n">
-        <v>6672324</v>
+        <v>6672286</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393624</v>
+        <v>122393598</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650798</v>
+        <v>650520</v>
       </c>
       <c r="R2" t="n">
-        <v>6672223</v>
+        <v>6671866</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393623</v>
+        <v>122393577</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,37 +815,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650805</v>
+        <v>650572</v>
       </c>
       <c r="R3" t="n">
-        <v>6672392</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393642</v>
+        <v>122393634</v>
       </c>
       <c r="B5" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,14 +1081,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650888</v>
+        <v>650818</v>
       </c>
       <c r="R5" t="n">
-        <v>6672343</v>
+        <v>6672400</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393651</v>
+        <v>122393647</v>
       </c>
       <c r="B6" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650521</v>
+        <v>650531</v>
       </c>
       <c r="R6" t="n">
-        <v>6671872</v>
+        <v>6671845</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393640</v>
+        <v>122393646</v>
       </c>
       <c r="B7" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,14 +1313,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650907</v>
+        <v>650560</v>
       </c>
       <c r="R7" t="n">
-        <v>6672335</v>
+        <v>6671817</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1337,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1392,7 @@
         <v>122393654</v>
       </c>
       <c r="B8" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1494,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393650</v>
+        <v>122393578</v>
       </c>
       <c r="B9" t="n">
-        <v>100503</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,27 +1525,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650527</v>
+        <v>650620</v>
       </c>
       <c r="R9" t="n">
-        <v>6671884</v>
+        <v>6671917</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1573,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393647</v>
+        <v>122393651</v>
       </c>
       <c r="B10" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1654,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650531</v>
+        <v>650521</v>
       </c>
       <c r="R10" t="n">
-        <v>6671845</v>
+        <v>6671872</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1689,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393634</v>
+        <v>122393617</v>
       </c>
       <c r="B11" t="n">
-        <v>100503</v>
+        <v>90833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,42 +1758,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650818</v>
+        <v>650568</v>
       </c>
       <c r="R11" t="n">
-        <v>6672400</v>
+        <v>6671929</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1805,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393611</v>
+        <v>122393670</v>
       </c>
       <c r="B12" t="n">
-        <v>90839</v>
+        <v>90605</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1873,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650587</v>
+        <v>650673</v>
       </c>
       <c r="R12" t="n">
-        <v>6671963</v>
+        <v>6672256</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1920,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1949,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393646</v>
+        <v>122393633</v>
       </c>
       <c r="B13" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,14 +2016,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650560</v>
+        <v>650806</v>
       </c>
       <c r="R13" t="n">
-        <v>6671817</v>
+        <v>6672399</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2036,7 +2055,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2065,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393617</v>
+        <v>122393650</v>
       </c>
       <c r="B14" t="n">
-        <v>90839</v>
+        <v>100506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,41 +2104,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650568</v>
+        <v>650527</v>
       </c>
       <c r="R14" t="n">
-        <v>6671929</v>
+        <v>6671884</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2151,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393598</v>
+        <v>122393632</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,50 +2220,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650520</v>
+        <v>650791</v>
       </c>
       <c r="R15" t="n">
-        <v>6671866</v>
+        <v>6672382</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2275,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2285,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393599</v>
+        <v>122390399</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,20 +2336,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2352,11 +2364,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2364,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650684</v>
+        <v>650718</v>
       </c>
       <c r="R16" t="n">
-        <v>6672094</v>
+        <v>6672218</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2399,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2409,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,14 +2440,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122390399</v>
+        <v>122393640</v>
       </c>
       <c r="B17" t="n">
-        <v>57753</v>
+        <v>100506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,45 +2464,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650718</v>
+        <v>650907</v>
       </c>
       <c r="R17" t="n">
-        <v>6672218</v>
+        <v>6672335</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,7 +2537,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,18 +2560,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393628</v>
+        <v>122393614</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>90833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,39 +2576,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2612,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650517</v>
+        <v>650587</v>
       </c>
       <c r="R18" t="n">
-        <v>6671888</v>
+        <v>6671907</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2647,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393635</v>
+        <v>122393619</v>
       </c>
       <c r="B19" t="n">
-        <v>100503</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2696,42 +2691,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650861</v>
+        <v>650561</v>
       </c>
       <c r="R19" t="n">
-        <v>6672364</v>
+        <v>6671937</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2763,7 +2757,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2767,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393636</v>
+        <v>122393611</v>
       </c>
       <c r="B20" t="n">
-        <v>100503</v>
+        <v>90833</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,42 +2806,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650878</v>
+        <v>650587</v>
       </c>
       <c r="R20" t="n">
-        <v>6672405</v>
+        <v>6671963</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2879,7 +2872,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2882,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2909,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393644</v>
+        <v>122393599</v>
       </c>
       <c r="B21" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,31 +2921,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2960,10 +2961,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650753</v>
+        <v>650684</v>
       </c>
       <c r="R21" t="n">
-        <v>6672196</v>
+        <v>6672094</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2995,7 +2996,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +3006,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393577</v>
+        <v>122393585</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,47 +3045,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650572</v>
+        <v>650587</v>
       </c>
       <c r="R22" t="n">
-        <v>6671983</v>
+        <v>6671916</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3116,7 +3120,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3126,7 +3130,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,10 +3157,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393653</v>
+        <v>122393642</v>
       </c>
       <c r="B23" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3193,14 +3197,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650726</v>
+        <v>650888</v>
       </c>
       <c r="R23" t="n">
-        <v>6672208</v>
+        <v>6672343</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3232,7 +3236,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,7 +3246,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,10 +3273,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393649</v>
+        <v>122393643</v>
       </c>
       <c r="B24" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3309,14 +3313,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650513</v>
+        <v>650851</v>
       </c>
       <c r="R24" t="n">
-        <v>6671875</v>
+        <v>6672282</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3358,7 +3362,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,10 +3389,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393610</v>
+        <v>122393589</v>
       </c>
       <c r="B25" t="n">
-        <v>90804</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3397,41 +3401,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650579</v>
+        <v>650540</v>
       </c>
       <c r="R25" t="n">
-        <v>6671979</v>
+        <v>6671903</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3463,7 +3476,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3473,7 +3486,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393585</v>
+        <v>122393628</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3512,39 +3525,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3552,10 +3565,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650587</v>
+        <v>650517</v>
       </c>
       <c r="R26" t="n">
-        <v>6671916</v>
+        <v>6671888</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3587,7 +3600,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3597,7 +3610,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3624,10 +3637,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393633</v>
+        <v>122393644</v>
       </c>
       <c r="B27" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3664,14 +3677,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650806</v>
+        <v>650753</v>
       </c>
       <c r="R27" t="n">
-        <v>6672399</v>
+        <v>6672196</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3703,7 +3716,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3713,7 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3740,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393619</v>
+        <v>122393610</v>
       </c>
       <c r="B28" t="n">
-        <v>90839</v>
+        <v>90798</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3752,25 +3765,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3783,10 +3796,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650561</v>
+        <v>650579</v>
       </c>
       <c r="R28" t="n">
-        <v>6671937</v>
+        <v>6671979</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3818,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3828,7 +3841,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,10 +3868,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393669</v>
+        <v>122393637</v>
       </c>
       <c r="B29" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3867,50 +3880,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650502</v>
+        <v>650982</v>
       </c>
       <c r="R29" t="n">
-        <v>6671865</v>
+        <v>6672324</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3942,7 +3947,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3952,7 +3957,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3979,7 +3984,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393589</v>
+        <v>122393669</v>
       </c>
       <c r="B30" t="n">
         <v>57399</v>
@@ -4021,20 +4026,20 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650540</v>
+        <v>650502</v>
       </c>
       <c r="R30" t="n">
-        <v>6671903</v>
+        <v>6671865</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4066,7 +4071,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4076,7 +4081,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4103,10 +4108,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393643</v>
+        <v>122393636</v>
       </c>
       <c r="B31" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4143,14 +4148,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650851</v>
+        <v>650878</v>
       </c>
       <c r="R31" t="n">
-        <v>6672282</v>
+        <v>6672405</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4182,7 +4187,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4192,7 +4197,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4219,10 +4224,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393614</v>
+        <v>122393624</v>
       </c>
       <c r="B32" t="n">
-        <v>90839</v>
+        <v>91453</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4231,25 +4236,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4258,14 +4263,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650587</v>
+        <v>650798</v>
       </c>
       <c r="R32" t="n">
-        <v>6671907</v>
+        <v>6672223</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4297,7 +4302,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4307,7 +4312,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4334,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393622</v>
+        <v>122393635</v>
       </c>
       <c r="B33" t="n">
-        <v>91230</v>
+        <v>100506</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4346,36 +4351,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650619</v>
+        <v>650861</v>
       </c>
       <c r="R33" t="n">
-        <v>6671913</v>
+        <v>6672364</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4407,7 +4418,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4417,7 +4428,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4444,10 +4455,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393632</v>
+        <v>122393649</v>
       </c>
       <c r="B34" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4484,14 +4495,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650791</v>
+        <v>650513</v>
       </c>
       <c r="R34" t="n">
-        <v>6672382</v>
+        <v>6671875</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4523,7 +4534,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4533,7 +4544,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4560,10 +4571,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393578</v>
+        <v>122393583</v>
       </c>
       <c r="B35" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4572,20 +4583,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4593,26 +4604,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650620</v>
+        <v>650841</v>
       </c>
       <c r="R35" t="n">
-        <v>6671917</v>
+        <v>6672286</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4644,7 +4658,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4654,7 +4668,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,10 +4695,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393670</v>
+        <v>122393653</v>
       </c>
       <c r="B36" t="n">
-        <v>90605</v>
+        <v>100506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4697,26 +4711,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4724,10 +4739,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650673</v>
+        <v>650726</v>
       </c>
       <c r="R36" t="n">
-        <v>6672256</v>
+        <v>6672208</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4759,7 +4774,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4769,7 +4784,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4796,10 +4811,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393637</v>
+        <v>122393622</v>
       </c>
       <c r="B37" t="n">
-        <v>100503</v>
+        <v>91231</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4808,42 +4823,36 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650982</v>
+        <v>650619</v>
       </c>
       <c r="R37" t="n">
-        <v>6672324</v>
+        <v>6671913</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4875,7 +4884,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4885,7 +4894,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4912,10 +4921,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393583</v>
+        <v>122393623</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>91453</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,50 +4933,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650841</v>
+        <v>650805</v>
       </c>
       <c r="R38" t="n">
-        <v>6672286</v>
+        <v>6672392</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393604</v>
+        <v>122393587</v>
       </c>
       <c r="B39" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5052,26 +5052,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650559</v>
+        <v>650580</v>
       </c>
       <c r="R39" t="n">
-        <v>6671894</v>
+        <v>6671917</v>
       </c>
       <c r="S39" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,12 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,10 +5284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5305,26 +5300,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5337,13 +5332,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R41" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,7 +5377,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393598</v>
+        <v>122393589</v>
       </c>
       <c r="B2" t="n">
         <v>57399</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650520</v>
+        <v>650540</v>
       </c>
       <c r="R2" t="n">
-        <v>6671866</v>
+        <v>6671903</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393577</v>
+        <v>122393619</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,36 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650572</v>
+        <v>650561</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671937</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393579</v>
+        <v>122393583</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,20 +926,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,26 +947,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650568</v>
+        <v>650841</v>
       </c>
       <c r="R4" t="n">
-        <v>6671816</v>
+        <v>6672286</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1004,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393634</v>
+        <v>122393633</v>
       </c>
       <c r="B5" t="n">
         <v>100506</v>
@@ -1085,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650818</v>
+        <v>650806</v>
       </c>
       <c r="R5" t="n">
-        <v>6672400</v>
+        <v>6672399</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1120,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393647</v>
+        <v>122393650</v>
       </c>
       <c r="B6" t="n">
         <v>100506</v>
@@ -1201,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650531</v>
+        <v>650527</v>
       </c>
       <c r="R6" t="n">
-        <v>6671845</v>
+        <v>6671884</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1236,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393646</v>
+        <v>122393636</v>
       </c>
       <c r="B7" t="n">
         <v>100506</v>
@@ -1313,14 +1310,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650560</v>
+        <v>650878</v>
       </c>
       <c r="R7" t="n">
-        <v>6671817</v>
+        <v>6672405</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1352,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393654</v>
+        <v>122393669</v>
       </c>
       <c r="B8" t="n">
-        <v>105346</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,35 +1398,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1437,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650496</v>
+        <v>650502</v>
       </c>
       <c r="R8" t="n">
-        <v>6671860</v>
+        <v>6671865</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1472,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1483,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393578</v>
+        <v>122393624</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>91453</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,43 +1526,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650620</v>
+        <v>650798</v>
       </c>
       <c r="R9" t="n">
-        <v>6671917</v>
+        <v>6672223</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1593,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,7 +1625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393651</v>
+        <v>122393642</v>
       </c>
       <c r="B10" t="n">
         <v>100506</v>
@@ -1670,14 +1665,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650521</v>
+        <v>650888</v>
       </c>
       <c r="R10" t="n">
-        <v>6671872</v>
+        <v>6672343</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1709,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393617</v>
+        <v>122393654</v>
       </c>
       <c r="B11" t="n">
-        <v>90833</v>
+        <v>105346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,41 +1753,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650568</v>
+        <v>650496</v>
       </c>
       <c r="R11" t="n">
-        <v>6671929</v>
+        <v>6671860</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393670</v>
+        <v>122393614</v>
       </c>
       <c r="B12" t="n">
-        <v>90605</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,25 +1873,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,14 +1900,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650673</v>
+        <v>650587</v>
       </c>
       <c r="R12" t="n">
-        <v>6672256</v>
+        <v>6671907</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393633</v>
+        <v>122393585</v>
       </c>
       <c r="B13" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,42 +1988,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650806</v>
+        <v>650587</v>
       </c>
       <c r="R13" t="n">
-        <v>6672399</v>
+        <v>6671916</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2055,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2065,7 +2073,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393650</v>
+        <v>122393628</v>
       </c>
       <c r="B14" t="n">
-        <v>100506</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,29 +2112,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2136,10 +2152,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650527</v>
+        <v>650517</v>
       </c>
       <c r="R14" t="n">
-        <v>6671884</v>
+        <v>6671888</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2171,7 +2187,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2197,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,7 +2224,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393632</v>
+        <v>122393634</v>
       </c>
       <c r="B15" t="n">
         <v>100506</v>
@@ -2248,14 +2264,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650791</v>
+        <v>650818</v>
       </c>
       <c r="R15" t="n">
-        <v>6672382</v>
+        <v>6672400</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2287,7 +2303,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2313,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2340,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122390399</v>
+        <v>122393644</v>
       </c>
       <c r="B16" t="n">
-        <v>57753</v>
+        <v>100506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,31 +2356,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2372,13 +2384,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650718</v>
+        <v>650753</v>
       </c>
       <c r="R16" t="n">
-        <v>6672218</v>
+        <v>6672196</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2407,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2429,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,11 +2452,7 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2564,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393614</v>
+        <v>122393577</v>
       </c>
       <c r="B18" t="n">
-        <v>90833</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,41 +2584,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650587</v>
+        <v>650572</v>
       </c>
       <c r="R18" t="n">
-        <v>6671907</v>
+        <v>6671983</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2642,7 +2656,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2666,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,10 +2693,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393619</v>
+        <v>122393598</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,37 +2709,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650561</v>
+        <v>650520</v>
       </c>
       <c r="R19" t="n">
-        <v>6671937</v>
+        <v>6671866</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2757,7 +2780,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2767,7 +2790,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2817,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393611</v>
+        <v>122393579</v>
       </c>
       <c r="B20" t="n">
-        <v>90833</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,41 +2829,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650587</v>
+        <v>650568</v>
       </c>
       <c r="R20" t="n">
-        <v>6671963</v>
+        <v>6671816</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2872,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2882,7 +2911,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2909,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393599</v>
+        <v>122393670</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>90605</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2921,39 +2950,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2961,10 +2981,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650684</v>
+        <v>650673</v>
       </c>
       <c r="R21" t="n">
-        <v>6672094</v>
+        <v>6672256</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2996,7 +3016,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3006,7 +3026,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3033,10 +3053,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393585</v>
+        <v>122393647</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,39 +3065,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3085,10 +3097,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650587</v>
+        <v>650531</v>
       </c>
       <c r="R22" t="n">
-        <v>6671916</v>
+        <v>6671845</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3120,7 +3132,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3130,7 +3142,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,10 +3169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393642</v>
+        <v>122393611</v>
       </c>
       <c r="B23" t="n">
-        <v>100506</v>
+        <v>90833</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3169,42 +3181,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650888</v>
+        <v>650587</v>
       </c>
       <c r="R23" t="n">
-        <v>6672343</v>
+        <v>6671963</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3236,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3246,7 +3257,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3273,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393643</v>
+        <v>122393610</v>
       </c>
       <c r="B24" t="n">
-        <v>100506</v>
+        <v>90798</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3289,27 +3300,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3317,10 +3327,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650851</v>
+        <v>650579</v>
       </c>
       <c r="R24" t="n">
-        <v>6672282</v>
+        <v>6671979</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3352,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3362,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3389,10 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393589</v>
+        <v>122393623</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>91453</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,50 +3411,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650540</v>
+        <v>650805</v>
       </c>
       <c r="R25" t="n">
-        <v>6671903</v>
+        <v>6672392</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3476,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3486,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393628</v>
+        <v>122393646</v>
       </c>
       <c r="B26" t="n">
-        <v>98240</v>
+        <v>100506</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,37 +3526,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3565,10 +3558,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650517</v>
+        <v>650560</v>
       </c>
       <c r="R26" t="n">
-        <v>6671888</v>
+        <v>6671817</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3600,7 +3593,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3610,7 +3603,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3637,7 +3630,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393644</v>
+        <v>122393651</v>
       </c>
       <c r="B27" t="n">
         <v>100506</v>
@@ -3677,14 +3670,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650753</v>
+        <v>650521</v>
       </c>
       <c r="R27" t="n">
-        <v>6672196</v>
+        <v>6671872</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3716,7 +3709,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3726,7 +3719,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3753,10 +3746,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393610</v>
+        <v>122393578</v>
       </c>
       <c r="B28" t="n">
-        <v>90798</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3769,37 +3762,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650579</v>
+        <v>650620</v>
       </c>
       <c r="R28" t="n">
-        <v>6671979</v>
+        <v>6671917</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3831,7 +3830,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,7 +3840,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3868,7 +3867,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393637</v>
+        <v>122393643</v>
       </c>
       <c r="B29" t="n">
         <v>100506</v>
@@ -3908,14 +3907,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650982</v>
+        <v>650851</v>
       </c>
       <c r="R29" t="n">
-        <v>6672324</v>
+        <v>6672282</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3947,7 +3946,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3957,7 +3956,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3984,10 +3983,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393669</v>
+        <v>122393622</v>
       </c>
       <c r="B30" t="n">
-        <v>57399</v>
+        <v>91231</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4000,46 +3999,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650502</v>
+        <v>650619</v>
       </c>
       <c r="R30" t="n">
-        <v>6671865</v>
+        <v>6671913</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4071,7 +4056,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4081,7 +4066,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4108,10 +4093,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393636</v>
+        <v>122393599</v>
       </c>
       <c r="B31" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4120,42 +4105,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650878</v>
+        <v>650684</v>
       </c>
       <c r="R31" t="n">
-        <v>6672405</v>
+        <v>6672094</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4187,7 +4180,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4197,7 +4190,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4224,10 +4217,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393624</v>
+        <v>122393632</v>
       </c>
       <c r="B32" t="n">
-        <v>91453</v>
+        <v>100506</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4240,37 +4233,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650798</v>
+        <v>650791</v>
       </c>
       <c r="R32" t="n">
-        <v>6672223</v>
+        <v>6672382</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4302,7 +4296,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4312,7 +4306,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4339,7 +4333,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393635</v>
+        <v>122393649</v>
       </c>
       <c r="B33" t="n">
         <v>100506</v>
@@ -4379,14 +4373,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650861</v>
+        <v>650513</v>
       </c>
       <c r="R33" t="n">
-        <v>6672364</v>
+        <v>6671875</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4418,7 +4412,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4428,7 +4422,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4455,10 +4449,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393649</v>
+        <v>122390399</v>
       </c>
       <c r="B34" t="n">
-        <v>100506</v>
+        <v>57753</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4471,41 +4465,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650513</v>
+        <v>650718</v>
       </c>
       <c r="R34" t="n">
-        <v>6671875</v>
+        <v>6672218</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4534,7 +4532,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4544,7 +4542,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4567,14 +4565,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393583</v>
+        <v>122393653</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4583,39 +4585,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4623,10 +4617,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650841</v>
+        <v>650726</v>
       </c>
       <c r="R35" t="n">
-        <v>6672286</v>
+        <v>6672208</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4658,7 +4652,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4668,7 +4662,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4695,7 +4689,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393653</v>
+        <v>122393635</v>
       </c>
       <c r="B36" t="n">
         <v>100506</v>
@@ -4735,14 +4729,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650726</v>
+        <v>650861</v>
       </c>
       <c r="R36" t="n">
-        <v>6672208</v>
+        <v>6672364</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4774,7 +4768,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4784,7 +4778,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4811,10 +4805,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393622</v>
+        <v>122393637</v>
       </c>
       <c r="B37" t="n">
-        <v>91231</v>
+        <v>100506</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4823,36 +4817,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650619</v>
+        <v>650982</v>
       </c>
       <c r="R37" t="n">
-        <v>6671913</v>
+        <v>6672324</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,10 +4921,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393623</v>
+        <v>122393617</v>
       </c>
       <c r="B38" t="n">
-        <v>91453</v>
+        <v>90833</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4933,25 +4933,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4960,14 +4960,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650805</v>
+        <v>650568</v>
       </c>
       <c r="R38" t="n">
-        <v>6672392</v>
+        <v>6671929</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393587</v>
+        <v>122393605</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,20 +5048,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650580</v>
+        <v>650566</v>
       </c>
       <c r="R39" t="n">
-        <v>6671917</v>
+        <v>6671827</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B40" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,20 +5172,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393589</v>
+        <v>122393577</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650540</v>
+        <v>650572</v>
       </c>
       <c r="R2" t="n">
-        <v>6671903</v>
+        <v>6671983</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393619</v>
+        <v>122393653</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>100507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650561</v>
+        <v>650726</v>
       </c>
       <c r="R3" t="n">
-        <v>6671937</v>
+        <v>6672208</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393583</v>
+        <v>122393637</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,50 +924,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650841</v>
+        <v>650982</v>
       </c>
       <c r="R4" t="n">
-        <v>6672286</v>
+        <v>6672324</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393633</v>
+        <v>122393632</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650806</v>
+        <v>650791</v>
       </c>
       <c r="R5" t="n">
-        <v>6672399</v>
+        <v>6672382</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393650</v>
+        <v>122393598</v>
       </c>
       <c r="B6" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,31 +1156,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1198,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650527</v>
+        <v>650520</v>
       </c>
       <c r="R6" t="n">
-        <v>6671884</v>
+        <v>6671866</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393636</v>
+        <v>122393624</v>
       </c>
       <c r="B7" t="n">
-        <v>100506</v>
+        <v>91454</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,38 +1284,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650878</v>
+        <v>650798</v>
       </c>
       <c r="R7" t="n">
-        <v>6672405</v>
+        <v>6672223</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1349,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393669</v>
+        <v>122393617</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,46 +1399,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650502</v>
+        <v>650568</v>
       </c>
       <c r="R8" t="n">
-        <v>6671865</v>
+        <v>6671929</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1473,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393624</v>
+        <v>122393634</v>
       </c>
       <c r="B9" t="n">
-        <v>91453</v>
+        <v>100507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,37 +1514,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650798</v>
+        <v>650818</v>
       </c>
       <c r="R9" t="n">
-        <v>6672223</v>
+        <v>6672400</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1588,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393642</v>
+        <v>122393623</v>
       </c>
       <c r="B10" t="n">
-        <v>100506</v>
+        <v>91454</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,38 +1630,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650888</v>
+        <v>650805</v>
       </c>
       <c r="R10" t="n">
-        <v>6672343</v>
+        <v>6672392</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1704,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393654</v>
+        <v>122393651</v>
       </c>
       <c r="B11" t="n">
-        <v>105346</v>
+        <v>100507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,42 +1745,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650496</v>
+        <v>650521</v>
       </c>
       <c r="R11" t="n">
-        <v>6671860</v>
+        <v>6671872</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1824,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393614</v>
+        <v>122393599</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,37 +1861,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650587</v>
+        <v>650684</v>
       </c>
       <c r="R12" t="n">
-        <v>6671907</v>
+        <v>6672094</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1939,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393585</v>
+        <v>122393670</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>90606</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,50 +1981,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650587</v>
+        <v>650673</v>
       </c>
       <c r="R13" t="n">
-        <v>6671916</v>
+        <v>6672256</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2063,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,7 +2087,7 @@
         <v>122393628</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2224,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393634</v>
+        <v>122393642</v>
       </c>
       <c r="B15" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2264,14 +2248,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650818</v>
+        <v>650888</v>
       </c>
       <c r="R15" t="n">
-        <v>6672400</v>
+        <v>6672343</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2303,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2313,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393644</v>
+        <v>122390399</v>
       </c>
       <c r="B16" t="n">
-        <v>100506</v>
+        <v>57754</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2356,27 +2340,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2384,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650753</v>
+        <v>650718</v>
       </c>
       <c r="R16" t="n">
-        <v>6672196</v>
+        <v>6672218</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2419,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,14 +2440,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393640</v>
+        <v>122393579</v>
       </c>
       <c r="B17" t="n">
-        <v>100506</v>
+        <v>5193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,38 +2464,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650907</v>
+        <v>650568</v>
       </c>
       <c r="R17" t="n">
-        <v>6672335</v>
+        <v>6671816</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2535,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2545,7 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393577</v>
+        <v>122393640</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>100507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2588,43 +2585,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650572</v>
+        <v>650907</v>
       </c>
       <c r="R18" t="n">
-        <v>6671983</v>
+        <v>6672335</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2656,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2666,7 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393598</v>
+        <v>122393646</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,39 +2697,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2745,10 +2729,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650520</v>
+        <v>650560</v>
       </c>
       <c r="R19" t="n">
-        <v>6671866</v>
+        <v>6671817</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2780,7 +2764,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2790,7 +2774,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2817,10 +2801,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393579</v>
+        <v>122393611</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>90834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2829,47 +2813,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650568</v>
+        <v>650587</v>
       </c>
       <c r="R20" t="n">
-        <v>6671816</v>
+        <v>6671963</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2901,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2911,7 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393670</v>
+        <v>122393636</v>
       </c>
       <c r="B21" t="n">
-        <v>90605</v>
+        <v>100507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2954,37 +2932,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650673</v>
+        <v>650878</v>
       </c>
       <c r="R21" t="n">
-        <v>6672256</v>
+        <v>6672405</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3016,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3026,7 +3005,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393647</v>
+        <v>122393585</v>
       </c>
       <c r="B22" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3065,31 +3044,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3097,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650531</v>
+        <v>650587</v>
       </c>
       <c r="R22" t="n">
-        <v>6671845</v>
+        <v>6671916</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3132,7 +3119,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3142,7 +3129,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393611</v>
+        <v>122393614</v>
       </c>
       <c r="B23" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,14 +3195,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
         <v>650587</v>
       </c>
       <c r="R23" t="n">
-        <v>6671963</v>
+        <v>6671907</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3247,7 +3234,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,7 +3244,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393610</v>
+        <v>122393622</v>
       </c>
       <c r="B24" t="n">
-        <v>90798</v>
+        <v>91232</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,25 +3283,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3323,14 +3305,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650579</v>
+        <v>650619</v>
       </c>
       <c r="R24" t="n">
-        <v>6671979</v>
+        <v>6671913</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3362,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3354,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,10 +3381,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393623</v>
+        <v>122393619</v>
       </c>
       <c r="B25" t="n">
-        <v>91453</v>
+        <v>90834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3411,25 +3393,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3438,14 +3420,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650805</v>
+        <v>650561</v>
       </c>
       <c r="R25" t="n">
-        <v>6672392</v>
+        <v>6671937</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3477,7 +3459,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3469,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393646</v>
+        <v>122393583</v>
       </c>
       <c r="B26" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3526,42 +3508,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650560</v>
+        <v>650841</v>
       </c>
       <c r="R26" t="n">
-        <v>6671817</v>
+        <v>6672286</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3593,7 +3583,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3603,7 +3593,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3630,10 +3620,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393651</v>
+        <v>122393635</v>
       </c>
       <c r="B27" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3670,14 +3660,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650521</v>
+        <v>650861</v>
       </c>
       <c r="R27" t="n">
-        <v>6671872</v>
+        <v>6672364</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3709,7 +3699,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3719,7 +3709,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,10 +3736,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393578</v>
+        <v>122393650</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>100507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3762,32 +3752,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3795,10 +3780,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650620</v>
+        <v>650527</v>
       </c>
       <c r="R28" t="n">
-        <v>6671917</v>
+        <v>6671884</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3830,7 +3815,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3840,7 +3825,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,7 +3855,7 @@
         <v>122393643</v>
       </c>
       <c r="B29" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3983,10 +3968,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393622</v>
+        <v>122393589</v>
       </c>
       <c r="B30" t="n">
-        <v>91231</v>
+        <v>57400</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3999,21 +3984,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4021,10 +4020,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650619</v>
+        <v>650540</v>
       </c>
       <c r="R30" t="n">
-        <v>6671913</v>
+        <v>6671903</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4056,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4066,7 +4065,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,10 +4092,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393599</v>
+        <v>122393669</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4135,20 +4134,20 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650684</v>
+        <v>650502</v>
       </c>
       <c r="R31" t="n">
-        <v>6672094</v>
+        <v>6671865</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4180,7 +4179,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4190,7 +4189,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,10 +4216,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393632</v>
+        <v>122393610</v>
       </c>
       <c r="B32" t="n">
-        <v>100506</v>
+        <v>90799</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,38 +4232,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650791</v>
+        <v>650579</v>
       </c>
       <c r="R32" t="n">
-        <v>6672382</v>
+        <v>6671979</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4296,7 +4294,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4306,7 +4304,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4333,10 +4331,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393649</v>
+        <v>122393633</v>
       </c>
       <c r="B33" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4373,14 +4371,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650513</v>
+        <v>650806</v>
       </c>
       <c r="R33" t="n">
-        <v>6671875</v>
+        <v>6672399</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4412,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4422,7 +4420,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4449,10 +4447,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122390399</v>
+        <v>122393649</v>
       </c>
       <c r="B34" t="n">
-        <v>57753</v>
+        <v>100507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4465,45 +4463,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650718</v>
+        <v>650513</v>
       </c>
       <c r="R34" t="n">
-        <v>6672218</v>
+        <v>6671875</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4532,7 +4526,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4542,7 +4536,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4565,18 +4559,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393653</v>
+        <v>122393644</v>
       </c>
       <c r="B35" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4617,10 +4607,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650726</v>
+        <v>650753</v>
       </c>
       <c r="R35" t="n">
-        <v>6672208</v>
+        <v>6672196</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4652,7 +4642,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4662,7 +4652,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4689,10 +4679,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393635</v>
+        <v>122393654</v>
       </c>
       <c r="B36" t="n">
-        <v>100506</v>
+        <v>105347</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4705,38 +4695,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650861</v>
+        <v>650496</v>
       </c>
       <c r="R36" t="n">
-        <v>6672364</v>
+        <v>6671860</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4768,7 +4762,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4778,7 +4772,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4805,10 +4799,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393637</v>
+        <v>122393578</v>
       </c>
       <c r="B37" t="n">
-        <v>100506</v>
+        <v>5193</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4821,38 +4815,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650982</v>
+        <v>650620</v>
       </c>
       <c r="R37" t="n">
-        <v>6672324</v>
+        <v>6671917</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4884,7 +4883,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4893,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,10 +4920,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393617</v>
+        <v>122393647</v>
       </c>
       <c r="B38" t="n">
-        <v>90833</v>
+        <v>100507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4933,41 +4932,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650568</v>
+        <v>650531</v>
       </c>
       <c r="R38" t="n">
-        <v>6671929</v>
+        <v>6671845</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393605</v>
+        <v>122393604</v>
       </c>
       <c r="B39" t="n">
-        <v>57753</v>
+        <v>57537</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,30 +5048,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650566</v>
+        <v>650559</v>
       </c>
       <c r="R39" t="n">
-        <v>6671827</v>
+        <v>6671894</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5165,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393587</v>
+        <v>122393605</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>57754</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,20 +5177,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5208,13 +5213,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650580</v>
+        <v>650566</v>
       </c>
       <c r="R40" t="n">
-        <v>6671917</v>
+        <v>6671827</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5284,10 +5289,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393604</v>
+        <v>122393587</v>
       </c>
       <c r="B41" t="n">
-        <v>57536</v>
+        <v>57400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,26 +5305,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5332,13 +5337,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650559</v>
+        <v>650580</v>
       </c>
       <c r="R41" t="n">
-        <v>6671894</v>
+        <v>6671917</v>
       </c>
       <c r="S41" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5377,12 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393598</v>
+        <v>122393624</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>91454</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,50 +1156,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650520</v>
+        <v>650798</v>
       </c>
       <c r="R6" t="n">
-        <v>6671866</v>
+        <v>6672223</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1231,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393624</v>
+        <v>122393617</v>
       </c>
       <c r="B7" t="n">
-        <v>91454</v>
+        <v>90834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,25 +1271,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650798</v>
+        <v>650568</v>
       </c>
       <c r="R7" t="n">
-        <v>6672223</v>
+        <v>6671929</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1346,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393617</v>
+        <v>122393598</v>
       </c>
       <c r="B8" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,37 +1390,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650568</v>
+        <v>650520</v>
       </c>
       <c r="R8" t="n">
-        <v>6671929</v>
+        <v>6671866</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393628</v>
+        <v>122393642</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>100507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,50 +2096,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650517</v>
+        <v>650888</v>
       </c>
       <c r="R14" t="n">
-        <v>6671888</v>
+        <v>6672343</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2171,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393642</v>
+        <v>122393628</v>
       </c>
       <c r="B15" t="n">
-        <v>100507</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,42 +2212,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650888</v>
+        <v>650517</v>
       </c>
       <c r="R15" t="n">
-        <v>6672343</v>
+        <v>6671888</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393611</v>
+        <v>122393585</v>
       </c>
       <c r="B20" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2817,37 +2817,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>650587</v>
       </c>
       <c r="R20" t="n">
-        <v>6671963</v>
+        <v>6671916</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2879,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393636</v>
+        <v>122393611</v>
       </c>
       <c r="B21" t="n">
-        <v>100507</v>
+        <v>90834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,42 +2937,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650878</v>
+        <v>650587</v>
       </c>
       <c r="R21" t="n">
-        <v>6672405</v>
+        <v>6671963</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +3013,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393585</v>
+        <v>122393636</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>100507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,50 +3052,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650587</v>
+        <v>650878</v>
       </c>
       <c r="R22" t="n">
-        <v>6671916</v>
+        <v>6672405</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393577</v>
+        <v>122393628</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650572</v>
+        <v>650517</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671888</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393653</v>
+        <v>122393650</v>
       </c>
       <c r="B3" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,14 +839,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650726</v>
+        <v>650527</v>
       </c>
       <c r="R3" t="n">
-        <v>6672208</v>
+        <v>6671884</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393637</v>
+        <v>122393653</v>
       </c>
       <c r="B4" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,14 +955,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650982</v>
+        <v>650726</v>
       </c>
       <c r="R4" t="n">
-        <v>6672324</v>
+        <v>6672208</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393632</v>
+        <v>122393614</v>
       </c>
       <c r="B5" t="n">
-        <v>100507</v>
+        <v>90837</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,42 +1043,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650791</v>
+        <v>650587</v>
       </c>
       <c r="R5" t="n">
-        <v>6672382</v>
+        <v>6671907</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1107,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393624</v>
+        <v>122390399</v>
       </c>
       <c r="B6" t="n">
-        <v>91454</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,26 +1162,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650798</v>
+        <v>650718</v>
       </c>
       <c r="R6" t="n">
-        <v>6672223</v>
+        <v>6672218</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,14 +1262,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>122393617</v>
       </c>
       <c r="B7" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393598</v>
+        <v>122393640</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,50 +1397,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650520</v>
+        <v>650907</v>
       </c>
       <c r="R8" t="n">
-        <v>6671866</v>
+        <v>6672335</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1461,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393634</v>
+        <v>122393670</v>
       </c>
       <c r="B9" t="n">
-        <v>100507</v>
+        <v>90609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,38 +1517,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650818</v>
+        <v>650673</v>
       </c>
       <c r="R9" t="n">
-        <v>6672400</v>
+        <v>6672256</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1577,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393623</v>
+        <v>122393636</v>
       </c>
       <c r="B10" t="n">
-        <v>91454</v>
+        <v>100510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,26 +1632,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650805</v>
+        <v>650878</v>
       </c>
       <c r="R10" t="n">
-        <v>6672392</v>
+        <v>6672405</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1692,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393651</v>
+        <v>122393610</v>
       </c>
       <c r="B11" t="n">
-        <v>100507</v>
+        <v>90802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,38 +1748,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650521</v>
+        <v>650579</v>
       </c>
       <c r="R11" t="n">
-        <v>6671872</v>
+        <v>6671979</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1808,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393599</v>
+        <v>122393579</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,20 +1859,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1878,29 +1880,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650684</v>
+        <v>650568</v>
       </c>
       <c r="R12" t="n">
-        <v>6672094</v>
+        <v>6671816</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1932,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1941,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393670</v>
+        <v>122393647</v>
       </c>
       <c r="B13" t="n">
-        <v>90606</v>
+        <v>100510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,37 +1984,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650673</v>
+        <v>650531</v>
       </c>
       <c r="R13" t="n">
-        <v>6672256</v>
+        <v>6671845</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393642</v>
+        <v>122393646</v>
       </c>
       <c r="B14" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,14 +2124,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650888</v>
+        <v>650560</v>
       </c>
       <c r="R14" t="n">
-        <v>6672343</v>
+        <v>6671817</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393628</v>
+        <v>122393599</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,50 +2212,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650517</v>
+        <v>650684</v>
       </c>
       <c r="R15" t="n">
-        <v>6671888</v>
+        <v>6672094</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122390399</v>
+        <v>122393624</v>
       </c>
       <c r="B16" t="n">
-        <v>57754</v>
+        <v>91457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,31 +2340,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2372,13 +2367,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650718</v>
+        <v>650798</v>
       </c>
       <c r="R16" t="n">
-        <v>6672218</v>
+        <v>6672223</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2407,7 +2402,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2412,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,18 +2435,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393579</v>
+        <v>122393644</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>100510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,43 +2455,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650568</v>
+        <v>650753</v>
       </c>
       <c r="R17" t="n">
-        <v>6671816</v>
+        <v>6672196</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2532,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2528,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393640</v>
+        <v>122393619</v>
       </c>
       <c r="B18" t="n">
-        <v>100507</v>
+        <v>90837</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,42 +2567,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650907</v>
+        <v>650561</v>
       </c>
       <c r="R18" t="n">
-        <v>6672335</v>
+        <v>6671937</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2648,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393646</v>
+        <v>122393577</v>
       </c>
       <c r="B19" t="n">
-        <v>100507</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,38 +2686,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650560</v>
+        <v>650572</v>
       </c>
       <c r="R19" t="n">
-        <v>6671817</v>
+        <v>6671983</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2764,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2774,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2801,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393585</v>
+        <v>122393651</v>
       </c>
       <c r="B20" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2813,39 +2803,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2853,10 +2835,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650587</v>
+        <v>650521</v>
       </c>
       <c r="R20" t="n">
-        <v>6671916</v>
+        <v>6671872</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2888,7 +2870,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2880,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2907,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393611</v>
+        <v>122393635</v>
       </c>
       <c r="B21" t="n">
-        <v>90834</v>
+        <v>100510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,41 +2919,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650587</v>
+        <v>650861</v>
       </c>
       <c r="R21" t="n">
-        <v>6671963</v>
+        <v>6672364</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3003,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,7 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393636</v>
+        <v>122393598</v>
       </c>
       <c r="B22" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,42 +3035,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650878</v>
+        <v>650520</v>
       </c>
       <c r="R22" t="n">
-        <v>6672405</v>
+        <v>6671866</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3119,7 +3110,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3120,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,10 +3147,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393614</v>
+        <v>122393578</v>
       </c>
       <c r="B23" t="n">
-        <v>90834</v>
+        <v>5193</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3168,30 +3159,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3199,10 +3196,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650587</v>
+        <v>650620</v>
       </c>
       <c r="R23" t="n">
-        <v>6671907</v>
+        <v>6671917</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3234,7 +3231,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3244,7 +3241,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393622</v>
+        <v>122393642</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>100510</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3283,36 +3280,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650619</v>
+        <v>650888</v>
       </c>
       <c r="R24" t="n">
-        <v>6671913</v>
+        <v>6672343</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3344,7 +3347,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,7 +3357,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3381,10 +3384,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393619</v>
+        <v>122393633</v>
       </c>
       <c r="B25" t="n">
-        <v>90834</v>
+        <v>100510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3393,41 +3396,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650561</v>
+        <v>650806</v>
       </c>
       <c r="R25" t="n">
-        <v>6671937</v>
+        <v>6672399</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3459,7 +3463,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3469,7 +3473,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3496,10 +3500,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393583</v>
+        <v>122393622</v>
       </c>
       <c r="B26" t="n">
-        <v>57400</v>
+        <v>91235</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3512,46 +3516,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650841</v>
+        <v>650619</v>
       </c>
       <c r="R26" t="n">
-        <v>6672286</v>
+        <v>6671913</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3583,7 +3573,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3593,7 +3583,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,10 +3610,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393635</v>
+        <v>122393583</v>
       </c>
       <c r="B27" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3632,42 +3622,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650861</v>
+        <v>650841</v>
       </c>
       <c r="R27" t="n">
-        <v>6672364</v>
+        <v>6672286</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3699,7 +3697,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3709,7 +3707,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3736,10 +3734,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393650</v>
+        <v>122393585</v>
       </c>
       <c r="B28" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3748,31 +3746,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3780,10 +3786,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650527</v>
+        <v>650587</v>
       </c>
       <c r="R28" t="n">
-        <v>6671884</v>
+        <v>6671916</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3815,7 +3821,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3825,7 +3831,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,7 +3861,7 @@
         <v>122393643</v>
       </c>
       <c r="B29" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3968,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393589</v>
+        <v>122393637</v>
       </c>
       <c r="B30" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3980,50 +3986,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650540</v>
+        <v>650982</v>
       </c>
       <c r="R30" t="n">
-        <v>6671903</v>
+        <v>6672324</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4055,7 +4053,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,7 +4063,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4092,10 +4090,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393669</v>
+        <v>122393623</v>
       </c>
       <c r="B31" t="n">
-        <v>57400</v>
+        <v>91457</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4104,50 +4102,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650502</v>
+        <v>650805</v>
       </c>
       <c r="R31" t="n">
-        <v>6671865</v>
+        <v>6672392</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4179,7 +4168,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4189,7 +4178,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4216,10 +4205,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393610</v>
+        <v>122393669</v>
       </c>
       <c r="B32" t="n">
-        <v>90799</v>
+        <v>57400</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4228,41 +4217,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650579</v>
+        <v>650502</v>
       </c>
       <c r="R32" t="n">
-        <v>6671979</v>
+        <v>6671865</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4294,7 +4292,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4304,7 +4302,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,10 +4329,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393633</v>
+        <v>122393649</v>
       </c>
       <c r="B33" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4371,14 +4369,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650806</v>
+        <v>650513</v>
       </c>
       <c r="R33" t="n">
-        <v>6672399</v>
+        <v>6671875</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4410,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4447,10 +4445,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393649</v>
+        <v>122393589</v>
       </c>
       <c r="B34" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4459,31 +4457,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4491,10 +4497,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650513</v>
+        <v>650540</v>
       </c>
       <c r="R34" t="n">
-        <v>6671875</v>
+        <v>6671903</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4526,7 +4532,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4536,7 +4542,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4563,10 +4569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393644</v>
+        <v>122393611</v>
       </c>
       <c r="B35" t="n">
-        <v>100507</v>
+        <v>90837</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4575,31 +4581,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4607,10 +4612,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650753</v>
+        <v>650587</v>
       </c>
       <c r="R35" t="n">
-        <v>6672196</v>
+        <v>6671963</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4642,7 +4647,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4652,7 +4657,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4679,10 +4684,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393654</v>
+        <v>122393634</v>
       </c>
       <c r="B36" t="n">
-        <v>105347</v>
+        <v>100510</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4695,42 +4700,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650496</v>
+        <v>650818</v>
       </c>
       <c r="R36" t="n">
-        <v>6671860</v>
+        <v>6672400</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4762,7 +4763,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4772,7 +4773,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4799,10 +4800,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393578</v>
+        <v>122393632</v>
       </c>
       <c r="B37" t="n">
-        <v>5193</v>
+        <v>100510</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4815,43 +4816,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650620</v>
+        <v>650791</v>
       </c>
       <c r="R37" t="n">
-        <v>6671917</v>
+        <v>6672382</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4883,7 +4879,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4893,7 +4889,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4920,10 +4916,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393647</v>
+        <v>122393654</v>
       </c>
       <c r="B38" t="n">
-        <v>100507</v>
+        <v>105350</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4936,38 +4932,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650531</v>
+        <v>650496</v>
       </c>
       <c r="R38" t="n">
-        <v>6671845</v>
+        <v>6671860</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B39" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,30 +5048,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R39" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S39" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,12 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5165,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B40" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5177,20 +5172,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5213,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,10 +5284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B41" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5305,26 +5300,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5337,13 +5332,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R41" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,7 +5377,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393628</v>
+        <v>122393614</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650517</v>
+        <v>650587</v>
       </c>
       <c r="R2" t="n">
-        <v>6671888</v>
+        <v>6671907</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393650</v>
+        <v>122393628</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,29 +802,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650527</v>
+        <v>650517</v>
       </c>
       <c r="R3" t="n">
-        <v>6671884</v>
+        <v>6671888</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393653</v>
+        <v>122393647</v>
       </c>
       <c r="B4" t="n">
         <v>100510</v>
@@ -955,14 +954,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650726</v>
+        <v>650531</v>
       </c>
       <c r="R4" t="n">
-        <v>6672208</v>
+        <v>6671845</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393614</v>
+        <v>122393654</v>
       </c>
       <c r="B5" t="n">
-        <v>90837</v>
+        <v>105350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,41 +1042,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650587</v>
+        <v>650496</v>
       </c>
       <c r="R5" t="n">
-        <v>6671907</v>
+        <v>6671860</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122390399</v>
+        <v>122393670</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>90609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1166,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650718</v>
+        <v>650673</v>
       </c>
       <c r="R6" t="n">
-        <v>6672218</v>
+        <v>6672256</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,18 +1261,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393617</v>
+        <v>122393579</v>
       </c>
       <c r="B7" t="n">
-        <v>90837</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,41 +1277,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>650568</v>
       </c>
       <c r="R7" t="n">
-        <v>6671929</v>
+        <v>6671816</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1348,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1386,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393640</v>
+        <v>122393632</v>
       </c>
       <c r="B8" t="n">
         <v>100510</v>
@@ -1425,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650907</v>
+        <v>650791</v>
       </c>
       <c r="R8" t="n">
-        <v>6672335</v>
+        <v>6672382</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1464,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393670</v>
+        <v>122393583</v>
       </c>
       <c r="B9" t="n">
-        <v>90609</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,30 +1514,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1544,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650673</v>
+        <v>650841</v>
       </c>
       <c r="R9" t="n">
-        <v>6672256</v>
+        <v>6672286</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1579,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393636</v>
+        <v>122393651</v>
       </c>
       <c r="B10" t="n">
         <v>100510</v>
@@ -1656,14 +1666,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650878</v>
+        <v>650521</v>
       </c>
       <c r="R10" t="n">
-        <v>6672405</v>
+        <v>6671872</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1695,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393610</v>
+        <v>122393599</v>
       </c>
       <c r="B11" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,30 +1754,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1775,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650579</v>
+        <v>650684</v>
       </c>
       <c r="R11" t="n">
-        <v>6671979</v>
+        <v>6672094</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1810,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1839,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393579</v>
+        <v>122393598</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,20 +1878,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1880,13 +1899,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1896,10 +1918,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650568</v>
+        <v>650520</v>
       </c>
       <c r="R12" t="n">
-        <v>6671816</v>
+        <v>6671866</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1931,7 +1953,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,7 +1963,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,7 +1990,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393647</v>
+        <v>122393649</v>
       </c>
       <c r="B13" t="n">
         <v>100510</v>
@@ -2012,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650531</v>
+        <v>650513</v>
       </c>
       <c r="R13" t="n">
-        <v>6671845</v>
+        <v>6671875</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2047,7 +2069,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2079,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,7 +2106,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393646</v>
+        <v>122393636</v>
       </c>
       <c r="B14" t="n">
         <v>100510</v>
@@ -2124,14 +2146,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650560</v>
+        <v>650878</v>
       </c>
       <c r="R14" t="n">
-        <v>6671817</v>
+        <v>6672405</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2163,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2173,7 +2195,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393599</v>
+        <v>122393619</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,35 +2238,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2252,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650684</v>
+        <v>650561</v>
       </c>
       <c r="R15" t="n">
-        <v>6672094</v>
+        <v>6671937</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2287,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393624</v>
+        <v>122393585</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,41 +2349,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650798</v>
+        <v>650587</v>
       </c>
       <c r="R16" t="n">
-        <v>6672223</v>
+        <v>6671916</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2402,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2412,7 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393644</v>
+        <v>122393624</v>
       </c>
       <c r="B17" t="n">
-        <v>100510</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,27 +2477,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2483,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650753</v>
+        <v>650798</v>
       </c>
       <c r="R17" t="n">
-        <v>6672196</v>
+        <v>6672223</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2518,7 +2539,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2528,7 +2549,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393619</v>
+        <v>122393637</v>
       </c>
       <c r="B18" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,41 +2588,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650561</v>
+        <v>650982</v>
       </c>
       <c r="R18" t="n">
-        <v>6671937</v>
+        <v>6672324</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2633,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2665,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393577</v>
+        <v>122393578</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2686,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2709,20 +2731,20 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650572</v>
+        <v>650620</v>
       </c>
       <c r="R19" t="n">
-        <v>6671983</v>
+        <v>6671917</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2754,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2786,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,7 +2813,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393651</v>
+        <v>122393653</v>
       </c>
       <c r="B20" t="n">
         <v>100510</v>
@@ -2831,14 +2853,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650521</v>
+        <v>650726</v>
       </c>
       <c r="R20" t="n">
-        <v>6671872</v>
+        <v>6672208</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2870,7 +2892,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2880,7 +2902,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,7 +2929,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393635</v>
+        <v>122393643</v>
       </c>
       <c r="B21" t="n">
         <v>100510</v>
@@ -2947,14 +2969,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650861</v>
+        <v>650851</v>
       </c>
       <c r="R21" t="n">
-        <v>6672364</v>
+        <v>6672282</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2986,7 +3008,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +3018,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393598</v>
+        <v>122393610</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>90802</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,50 +3057,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650520</v>
+        <v>650579</v>
       </c>
       <c r="R22" t="n">
-        <v>6671866</v>
+        <v>6671979</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3110,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3120,7 +3133,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,10 +3160,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393578</v>
+        <v>122393611</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>90837</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3159,47 +3172,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650620</v>
+        <v>650587</v>
       </c>
       <c r="R23" t="n">
-        <v>6671917</v>
+        <v>6671963</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3231,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3241,7 +3248,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3268,7 +3275,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393642</v>
+        <v>122393635</v>
       </c>
       <c r="B24" t="n">
         <v>100510</v>
@@ -3308,14 +3315,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650888</v>
+        <v>650861</v>
       </c>
       <c r="R24" t="n">
-        <v>6672343</v>
+        <v>6672364</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3347,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3357,7 +3364,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3384,7 +3391,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393633</v>
+        <v>122393634</v>
       </c>
       <c r="B25" t="n">
         <v>100510</v>
@@ -3428,10 +3435,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650806</v>
+        <v>650818</v>
       </c>
       <c r="R25" t="n">
-        <v>6672399</v>
+        <v>6672400</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3463,7 +3470,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3473,7 +3480,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393622</v>
+        <v>122393617</v>
       </c>
       <c r="B26" t="n">
-        <v>91235</v>
+        <v>90837</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3516,16 +3523,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3534,14 +3546,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650619</v>
+        <v>650568</v>
       </c>
       <c r="R26" t="n">
-        <v>6671913</v>
+        <v>6671929</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3573,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3583,7 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393583</v>
+        <v>122393633</v>
       </c>
       <c r="B27" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3622,50 +3634,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650841</v>
+        <v>650806</v>
       </c>
       <c r="R27" t="n">
-        <v>6672286</v>
+        <v>6672399</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3697,7 +3701,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3707,7 +3711,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3734,10 +3738,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393585</v>
+        <v>122393622</v>
       </c>
       <c r="B28" t="n">
-        <v>57400</v>
+        <v>91235</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3750,35 +3754,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3786,10 +3776,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650587</v>
+        <v>650619</v>
       </c>
       <c r="R28" t="n">
-        <v>6671916</v>
+        <v>6671913</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3821,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3831,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393643</v>
+        <v>122393577</v>
       </c>
       <c r="B29" t="n">
-        <v>100510</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3874,27 +3864,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3902,10 +3897,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650851</v>
+        <v>650572</v>
       </c>
       <c r="R29" t="n">
-        <v>6672282</v>
+        <v>6671983</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3937,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3947,7 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3974,7 +3969,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393637</v>
+        <v>122393640</v>
       </c>
       <c r="B30" t="n">
         <v>100510</v>
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650982</v>
+        <v>650907</v>
       </c>
       <c r="R30" t="n">
-        <v>6672324</v>
+        <v>6672335</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4053,7 +4048,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4063,7 +4058,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,10 +4085,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393623</v>
+        <v>122393650</v>
       </c>
       <c r="B31" t="n">
-        <v>91457</v>
+        <v>100510</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4106,37 +4101,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650805</v>
+        <v>650527</v>
       </c>
       <c r="R31" t="n">
-        <v>6672392</v>
+        <v>6671884</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4168,7 +4164,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4178,7 +4174,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4329,7 +4325,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393649</v>
+        <v>122393642</v>
       </c>
       <c r="B33" t="n">
         <v>100510</v>
@@ -4369,14 +4365,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650513</v>
+        <v>650888</v>
       </c>
       <c r="R33" t="n">
-        <v>6671875</v>
+        <v>6672343</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4408,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4414,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,10 +4441,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393589</v>
+        <v>122393646</v>
       </c>
       <c r="B34" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4457,39 +4453,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4497,10 +4485,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650540</v>
+        <v>650560</v>
       </c>
       <c r="R34" t="n">
-        <v>6671903</v>
+        <v>6671817</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4532,7 +4520,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4542,7 +4530,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4569,10 +4557,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393611</v>
+        <v>122393589</v>
       </c>
       <c r="B35" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4585,37 +4573,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650587</v>
+        <v>650540</v>
       </c>
       <c r="R35" t="n">
-        <v>6671963</v>
+        <v>6671903</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4647,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4657,7 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4684,10 +4681,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393634</v>
+        <v>122390399</v>
       </c>
       <c r="B36" t="n">
-        <v>100510</v>
+        <v>57754</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4700,41 +4697,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650818</v>
+        <v>650718</v>
       </c>
       <c r="R36" t="n">
-        <v>6672400</v>
+        <v>6672218</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4763,7 +4764,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4773,7 +4774,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4796,14 +4797,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393632</v>
+        <v>122393623</v>
       </c>
       <c r="B37" t="n">
-        <v>100510</v>
+        <v>91457</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4816,38 +4821,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650791</v>
+        <v>650805</v>
       </c>
       <c r="R37" t="n">
-        <v>6672382</v>
+        <v>6672392</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4879,7 +4883,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4889,7 +4893,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4916,10 +4920,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393654</v>
+        <v>122393644</v>
       </c>
       <c r="B38" t="n">
-        <v>105350</v>
+        <v>100510</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4932,42 +4936,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650496</v>
+        <v>650753</v>
       </c>
       <c r="R38" t="n">
-        <v>6671860</v>
+        <v>6672196</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393605</v>
+        <v>122393587</v>
       </c>
       <c r="B39" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5048,20 +5048,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650566</v>
+        <v>650580</v>
       </c>
       <c r="R39" t="n">
-        <v>6671827</v>
+        <v>6671917</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393587</v>
+        <v>122393604</v>
       </c>
       <c r="B40" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650580</v>
+        <v>650559</v>
       </c>
       <c r="R40" t="n">
-        <v>6671917</v>
+        <v>6671894</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,7 +5253,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5284,10 +5289,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393604</v>
+        <v>122393605</v>
       </c>
       <c r="B41" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5296,30 +5301,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5332,13 +5337,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650559</v>
+        <v>650566</v>
       </c>
       <c r="R41" t="n">
-        <v>6671894</v>
+        <v>6671827</v>
       </c>
       <c r="S41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5377,12 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393583</v>
+        <v>122393651</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,50 +1514,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650841</v>
+        <v>650521</v>
       </c>
       <c r="R9" t="n">
-        <v>6672286</v>
+        <v>6671872</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1589,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1591,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393651</v>
+        <v>122393583</v>
       </c>
       <c r="B10" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,42 +1630,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650521</v>
+        <v>650841</v>
       </c>
       <c r="R10" t="n">
-        <v>6671872</v>
+        <v>6672286</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393619</v>
+        <v>122393585</v>
       </c>
       <c r="B15" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,37 +2238,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650561</v>
+        <v>650587</v>
       </c>
       <c r="R15" t="n">
-        <v>6671937</v>
+        <v>6671916</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2300,7 +2309,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2319,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393585</v>
+        <v>122393619</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,46 +2362,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650587</v>
+        <v>650561</v>
       </c>
       <c r="R16" t="n">
-        <v>6671916</v>
+        <v>6671937</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393634</v>
+        <v>122393617</v>
       </c>
       <c r="B25" t="n">
-        <v>100510</v>
+        <v>90837</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,42 +3403,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650818</v>
+        <v>650568</v>
       </c>
       <c r="R25" t="n">
-        <v>6672400</v>
+        <v>6671929</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3470,7 +3469,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3480,7 +3479,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3507,10 +3506,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393617</v>
+        <v>122393634</v>
       </c>
       <c r="B26" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3519,41 +3518,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650568</v>
+        <v>650818</v>
       </c>
       <c r="R26" t="n">
-        <v>6671929</v>
+        <v>6672400</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393633</v>
+        <v>122393622</v>
       </c>
       <c r="B27" t="n">
-        <v>100510</v>
+        <v>91235</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3634,42 +3634,36 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650806</v>
+        <v>650619</v>
       </c>
       <c r="R27" t="n">
-        <v>6672399</v>
+        <v>6671913</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3701,7 +3695,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3711,7 +3705,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3738,10 +3732,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393622</v>
+        <v>122393577</v>
       </c>
       <c r="B28" t="n">
-        <v>91235</v>
+        <v>5173</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3750,36 +3744,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650619</v>
+        <v>650572</v>
       </c>
       <c r="R28" t="n">
-        <v>6671913</v>
+        <v>6671983</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3811,7 +3816,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3821,7 +3826,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3848,10 +3853,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393577</v>
+        <v>122393633</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>100510</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3864,43 +3869,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650572</v>
+        <v>650806</v>
       </c>
       <c r="R29" t="n">
-        <v>6671983</v>
+        <v>6672399</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393651</v>
+        <v>122393583</v>
       </c>
       <c r="B9" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,42 +1514,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650521</v>
+        <v>650841</v>
       </c>
       <c r="R9" t="n">
-        <v>6671872</v>
+        <v>6672286</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1581,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393583</v>
+        <v>122393651</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,50 +1638,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650841</v>
+        <v>650521</v>
       </c>
       <c r="R10" t="n">
-        <v>6672286</v>
+        <v>6671872</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3045,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393610</v>
+        <v>122393635</v>
       </c>
       <c r="B22" t="n">
-        <v>90802</v>
+        <v>100510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,37 +3061,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650579</v>
+        <v>650861</v>
       </c>
       <c r="R22" t="n">
-        <v>6671979</v>
+        <v>6672364</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3123,7 +3124,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,7 +3134,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3275,10 +3276,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393635</v>
+        <v>122393610</v>
       </c>
       <c r="B24" t="n">
-        <v>100510</v>
+        <v>90802</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,38 +3292,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650861</v>
+        <v>650579</v>
       </c>
       <c r="R24" t="n">
-        <v>6672364</v>
+        <v>6671979</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3622,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393622</v>
+        <v>122393633</v>
       </c>
       <c r="B27" t="n">
-        <v>91235</v>
+        <v>100510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3634,36 +3634,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650619</v>
+        <v>650806</v>
       </c>
       <c r="R27" t="n">
-        <v>6671913</v>
+        <v>6672399</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3695,7 +3701,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3705,7 +3711,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3732,10 +3738,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393577</v>
+        <v>122393622</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>91235</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3744,47 +3750,36 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650572</v>
+        <v>650619</v>
       </c>
       <c r="R28" t="n">
-        <v>6671983</v>
+        <v>6671913</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3816,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3826,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,10 +3848,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393633</v>
+        <v>122393577</v>
       </c>
       <c r="B29" t="n">
-        <v>100510</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3869,38 +3864,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650806</v>
+        <v>650572</v>
       </c>
       <c r="R29" t="n">
-        <v>6672399</v>
+        <v>6671983</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393583</v>
+        <v>122393651</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,50 +1514,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650841</v>
+        <v>650521</v>
       </c>
       <c r="R9" t="n">
-        <v>6672286</v>
+        <v>6671872</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1589,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1591,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393651</v>
+        <v>122393583</v>
       </c>
       <c r="B10" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,42 +1630,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650521</v>
+        <v>650841</v>
       </c>
       <c r="R10" t="n">
-        <v>6671872</v>
+        <v>6672286</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3045,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393635</v>
+        <v>122393610</v>
       </c>
       <c r="B22" t="n">
-        <v>100510</v>
+        <v>90802</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,38 +3061,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650861</v>
+        <v>650579</v>
       </c>
       <c r="R22" t="n">
-        <v>6672364</v>
+        <v>6671979</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3124,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3134,7 +3133,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,10 +3275,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393610</v>
+        <v>122393635</v>
       </c>
       <c r="B24" t="n">
-        <v>90802</v>
+        <v>100510</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3292,37 +3291,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650579</v>
+        <v>650861</v>
       </c>
       <c r="R24" t="n">
-        <v>6671979</v>
+        <v>6672364</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393617</v>
+        <v>122393634</v>
       </c>
       <c r="B25" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,41 +3403,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650568</v>
+        <v>650818</v>
       </c>
       <c r="R25" t="n">
-        <v>6671929</v>
+        <v>6672400</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3479,7 +3480,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393634</v>
+        <v>122393617</v>
       </c>
       <c r="B26" t="n">
-        <v>100510</v>
+        <v>90837</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,42 +3519,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650818</v>
+        <v>650568</v>
       </c>
       <c r="R26" t="n">
-        <v>6672400</v>
+        <v>6671929</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393633</v>
+        <v>122393622</v>
       </c>
       <c r="B27" t="n">
-        <v>100510</v>
+        <v>91235</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3634,42 +3634,36 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650806</v>
+        <v>650619</v>
       </c>
       <c r="R27" t="n">
-        <v>6672399</v>
+        <v>6671913</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3701,7 +3695,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3711,7 +3705,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3738,10 +3732,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393622</v>
+        <v>122393577</v>
       </c>
       <c r="B28" t="n">
-        <v>91235</v>
+        <v>5173</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3750,36 +3744,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650619</v>
+        <v>650572</v>
       </c>
       <c r="R28" t="n">
-        <v>6671913</v>
+        <v>6671983</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3811,7 +3816,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3821,7 +3826,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3848,10 +3853,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393577</v>
+        <v>122393633</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>100510</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3864,43 +3869,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650572</v>
+        <v>650806</v>
       </c>
       <c r="R29" t="n">
-        <v>6671983</v>
+        <v>6672399</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -3391,10 +3391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393634</v>
+        <v>122393617</v>
       </c>
       <c r="B25" t="n">
-        <v>100510</v>
+        <v>90837</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,42 +3403,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650818</v>
+        <v>650568</v>
       </c>
       <c r="R25" t="n">
-        <v>6672400</v>
+        <v>6671929</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3470,7 +3469,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3480,7 +3479,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3507,10 +3506,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393617</v>
+        <v>122393634</v>
       </c>
       <c r="B26" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3519,41 +3518,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650568</v>
+        <v>650818</v>
       </c>
       <c r="R26" t="n">
-        <v>6671929</v>
+        <v>6672400</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393622</v>
+        <v>122393633</v>
       </c>
       <c r="B27" t="n">
-        <v>91235</v>
+        <v>100510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3634,36 +3634,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650619</v>
+        <v>650806</v>
       </c>
       <c r="R27" t="n">
-        <v>6671913</v>
+        <v>6672399</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3695,7 +3701,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3705,7 +3711,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3732,10 +3738,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393577</v>
+        <v>122393622</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>91235</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3744,47 +3750,36 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650572</v>
+        <v>650619</v>
       </c>
       <c r="R28" t="n">
-        <v>6671983</v>
+        <v>6671913</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3816,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3826,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,10 +3848,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393633</v>
+        <v>122393577</v>
       </c>
       <c r="B29" t="n">
-        <v>100510</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3869,38 +3864,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650806</v>
+        <v>650572</v>
       </c>
       <c r="R29" t="n">
-        <v>6672399</v>
+        <v>6671983</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393614</v>
+        <v>122393628</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650587</v>
+        <v>650517</v>
       </c>
       <c r="R2" t="n">
-        <v>6671907</v>
+        <v>6671888</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393628</v>
+        <v>122393614</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650517</v>
+        <v>650587</v>
       </c>
       <c r="R3" t="n">
-        <v>6671888</v>
+        <v>6671907</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393585</v>
+        <v>122393619</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,46 +2238,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650587</v>
+        <v>650561</v>
       </c>
       <c r="R15" t="n">
-        <v>6671916</v>
+        <v>6671937</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2309,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2319,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393619</v>
+        <v>122393585</v>
       </c>
       <c r="B16" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,37 +2353,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650561</v>
+        <v>650587</v>
       </c>
       <c r="R16" t="n">
-        <v>6671937</v>
+        <v>6671916</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393617</v>
+        <v>122393634</v>
       </c>
       <c r="B25" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3403,41 +3403,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650568</v>
+        <v>650818</v>
       </c>
       <c r="R25" t="n">
-        <v>6671929</v>
+        <v>6672400</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3479,7 +3480,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393634</v>
+        <v>122393617</v>
       </c>
       <c r="B26" t="n">
-        <v>100510</v>
+        <v>90837</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,42 +3519,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650818</v>
+        <v>650568</v>
       </c>
       <c r="R26" t="n">
-        <v>6672400</v>
+        <v>6671929</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5411,6 +5411,111 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126575818</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95964</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vretfallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>650528</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6671866</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -5416,7 +5416,7 @@
         <v>126575818</v>
       </c>
       <c r="B42" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -5416,7 +5416,7 @@
         <v>126575818</v>
       </c>
       <c r="B42" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -5416,7 +5416,7 @@
         <v>126575818</v>
       </c>
       <c r="B42" t="n">
-        <v>96045</v>
+        <v>96039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122393578</v>
+        <v>122393611</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650620</v>
+        <v>650587</v>
       </c>
       <c r="R2" t="n">
-        <v>6671917</v>
+        <v>6671963</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,54 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122393644</v>
+        <v>122393614</v>
       </c>
       <c r="B3" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650753</v>
+        <v>650587</v>
       </c>
       <c r="R3" t="n">
-        <v>6672196</v>
+        <v>6671907</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393585</v>
+        <v>122393617</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,46 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650587</v>
+        <v>650568</v>
       </c>
       <c r="R4" t="n">
-        <v>6671916</v>
+        <v>6671929</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -999,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,61 +1005,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122390399</v>
+        <v>122393618</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650718</v>
+        <v>650580</v>
       </c>
       <c r="R5" t="n">
-        <v>6672218</v>
+        <v>6671807</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,45 +1111,36 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393623</v>
+        <v>122393619</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,14 +1149,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650805</v>
+        <v>650561</v>
       </c>
       <c r="R6" t="n">
-        <v>6672392</v>
+        <v>6671937</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,56 +1225,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393611</v>
+        <v>126575818</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650587</v>
+        <v>650528</v>
       </c>
       <c r="R7" t="n">
-        <v>6671963</v>
+        <v>6671866</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,22 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,74 +1318,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393598</v>
+        <v>122393670</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650520</v>
+        <v>650673</v>
       </c>
       <c r="R8" t="n">
-        <v>6671866</v>
+        <v>6672256</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1477,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,51 +1440,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393583</v>
+        <v>122393610</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1566,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650841</v>
+        <v>650579</v>
       </c>
       <c r="R9" t="n">
-        <v>6672286</v>
+        <v>6671979</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1601,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,15 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393670</v>
+        <v>122393585</v>
       </c>
       <c r="B10" t="n">
-        <v>90712</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,37 +1561,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650673</v>
+        <v>650587</v>
       </c>
       <c r="R10" t="n">
-        <v>6672256</v>
+        <v>6671916</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1716,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,19 +1669,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393599</v>
+        <v>122393587</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1793,22 +1704,18 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650684</v>
+        <v>650580</v>
       </c>
       <c r="R11" t="n">
-        <v>6672094</v>
+        <v>6671917</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1840,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,23 +1780,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>122393589</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2001,15 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122393649</v>
+        <v>122393598</v>
       </c>
       <c r="B13" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,27 +1918,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2045,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650513</v>
+        <v>650520</v>
       </c>
       <c r="R13" t="n">
-        <v>6671875</v>
+        <v>6671866</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2080,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2090,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,15 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122393637</v>
+        <v>122393599</v>
       </c>
       <c r="B14" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,38 +2037,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650982</v>
+        <v>650684</v>
       </c>
       <c r="R14" t="n">
-        <v>6672324</v>
+        <v>6672094</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2196,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2206,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,15 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122393651</v>
+        <v>122393669</v>
       </c>
       <c r="B15" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,38 +2156,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650521</v>
+        <v>650502</v>
       </c>
       <c r="R15" t="n">
-        <v>6671872</v>
+        <v>6671865</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2312,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2322,7 +2237,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,48 +2264,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122393622</v>
+        <v>122393577</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650619</v>
+        <v>650572</v>
       </c>
       <c r="R16" t="n">
-        <v>6671913</v>
+        <v>6671983</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2422,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2432,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,15 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122393633</v>
+        <v>122390399</v>
       </c>
       <c r="B17" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,41 +2391,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650806</v>
+        <v>650718</v>
       </c>
       <c r="R17" t="n">
-        <v>6672399</v>
+        <v>6672218</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,60 +2491,64 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122393617</v>
+        <v>122393605</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650568</v>
+        <v>650566</v>
       </c>
       <c r="R18" t="n">
-        <v>6671929</v>
+        <v>6671827</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,66 +2610,64 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122393577</v>
+        <v>122393604</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650572</v>
+        <v>650559</v>
       </c>
       <c r="R19" t="n">
-        <v>6671983</v>
+        <v>6671894</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2774,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,7 +2706,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,19 +2734,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122393636</v>
+        <v>122393578</v>
       </c>
       <c r="B20" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,38 +2753,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650878</v>
+        <v>650620</v>
       </c>
       <c r="R20" t="n">
-        <v>6672405</v>
+        <v>6671917</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2890,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,15 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122393640</v>
+        <v>122393579</v>
       </c>
       <c r="B21" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,38 +2869,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650907</v>
+        <v>650568</v>
       </c>
       <c r="R21" t="n">
-        <v>6672335</v>
+        <v>6671816</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3006,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,62 +2974,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122393669</v>
+        <v>122393628</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650502</v>
+        <v>650517</v>
       </c>
       <c r="R22" t="n">
-        <v>6671865</v>
+        <v>6671888</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3130,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,15 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122393579</v>
+        <v>122393654</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,43 +3104,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650568</v>
+        <v>650496</v>
       </c>
       <c r="R23" t="n">
-        <v>6671816</v>
+        <v>6671860</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3251,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,15 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122393643</v>
+        <v>122393646</v>
       </c>
       <c r="B24" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3328,14 +3243,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650851</v>
+        <v>650560</v>
       </c>
       <c r="R24" t="n">
-        <v>6672282</v>
+        <v>6671817</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3367,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3377,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3404,49 +3319,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122393628</v>
+        <v>122393647</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3456,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650517</v>
+        <v>650531</v>
       </c>
       <c r="R25" t="n">
-        <v>6671888</v>
+        <v>6671845</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3491,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,15 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122393624</v>
+        <v>122393649</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3544,37 +3441,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650798</v>
+        <v>650513</v>
       </c>
       <c r="R26" t="n">
-        <v>6672223</v>
+        <v>6671875</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3606,7 +3504,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3616,7 +3514,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3643,15 +3541,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122393632</v>
+        <v>122393650</v>
       </c>
       <c r="B27" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3683,14 +3576,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vargstensbottnen, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650791</v>
+        <v>650527</v>
       </c>
       <c r="R27" t="n">
-        <v>6672382</v>
+        <v>6671884</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3722,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3732,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3759,15 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122393610</v>
+        <v>122393651</v>
       </c>
       <c r="B28" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,37 +3663,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650579</v>
+        <v>650521</v>
       </c>
       <c r="R28" t="n">
-        <v>6671979</v>
+        <v>6671872</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3837,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3847,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,15 +3763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122393634</v>
+        <v>122393652</v>
       </c>
       <c r="B29" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,14 +3798,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Ersbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650818</v>
+        <v>650713</v>
       </c>
       <c r="R29" t="n">
-        <v>6672400</v>
+        <v>6672174</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3953,7 +3837,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3963,7 +3847,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,57 +3874,55 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122393653</v>
+        <v>126575816</v>
       </c>
       <c r="B30" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>230405</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Vretfallet, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650726</v>
+        <v>650658</v>
       </c>
       <c r="R30" t="n">
-        <v>6672208</v>
+        <v>6672028</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4064,22 +3946,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ett helt träd</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,55 +3971,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122393646</v>
+        <v>122393622</v>
       </c>
       <c r="B31" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4150,10 +4021,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650560</v>
+        <v>650619</v>
       </c>
       <c r="R31" t="n">
-        <v>6671817</v>
+        <v>6671913</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4185,7 +4056,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,7 +4066,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4222,15 +4093,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122393635</v>
+        <v>122393623</v>
       </c>
       <c r="B32" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,27 +4104,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4266,10 +4131,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650861</v>
+        <v>650805</v>
       </c>
       <c r="R32" t="n">
-        <v>6672364</v>
+        <v>6672392</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4301,7 +4166,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4176,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,15 +4203,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122393650</v>
+        <v>122393624</v>
       </c>
       <c r="B33" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4354,38 +4214,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650527</v>
+        <v>650798</v>
       </c>
       <c r="R33" t="n">
-        <v>6671884</v>
+        <v>6672223</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4417,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4427,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4454,15 +4313,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122393642</v>
+        <v>122393583</v>
       </c>
       <c r="B34" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4470,38 +4324,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Marhällsbottnen, Upl</t>
+          <t>Fulmyren, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650888</v>
+        <v>650841</v>
       </c>
       <c r="R34" t="n">
-        <v>6672343</v>
+        <v>6672286</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4533,7 +4395,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,7 +4405,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4570,15 +4432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122393647</v>
+        <v>122393632</v>
       </c>
       <c r="B35" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,14 +4467,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Vargstensbottnen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650531</v>
+        <v>650791</v>
       </c>
       <c r="R35" t="n">
-        <v>6671845</v>
+        <v>6672382</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4649,7 +4506,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4659,7 +4516,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4686,15 +4543,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122393654</v>
+        <v>122393633</v>
       </c>
       <c r="B36" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,42 +4554,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650496</v>
+        <v>650806</v>
       </c>
       <c r="R36" t="n">
-        <v>6671860</v>
+        <v>6672399</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4769,7 +4617,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4779,7 +4627,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4806,53 +4654,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122393619</v>
+        <v>122393634</v>
       </c>
       <c r="B37" t="n">
-        <v>90940</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fulmyren, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650561</v>
+        <v>650818</v>
       </c>
       <c r="R37" t="n">
-        <v>6671937</v>
+        <v>6672400</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4884,7 +4728,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,7 +4738,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,53 +4765,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122393614</v>
+        <v>122393635</v>
       </c>
       <c r="B38" t="n">
-        <v>90940</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650587</v>
+        <v>650861</v>
       </c>
       <c r="R38" t="n">
-        <v>6671907</v>
+        <v>6672364</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4999,7 +4839,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +4849,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5036,58 +4876,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122393587</v>
+        <v>122393636</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Per-Ersbottnen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650580</v>
+        <v>650878</v>
       </c>
       <c r="R39" t="n">
-        <v>6671917</v>
+        <v>6672405</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5119,7 +4950,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +4960,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5152,23 +4983,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122393605</v>
+        <v>122393637</v>
       </c>
       <c r="B40" t="n">
-        <v>57848</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,45 +4998,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650566</v>
+        <v>650982</v>
       </c>
       <c r="R40" t="n">
-        <v>6671827</v>
+        <v>6672324</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5243,7 +5061,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5253,7 +5071,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5276,69 +5094,56 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122393604</v>
+        <v>122393640</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650559</v>
+        <v>650907</v>
       </c>
       <c r="R41" t="n">
-        <v>6671894</v>
+        <v>6672335</v>
       </c>
       <c r="S41" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5367,7 +5172,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5377,12 +5182,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Förmodligen samma par som hördes lite längre västerut en stund tidigare.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,18 +5205,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126575818</v>
+        <v>122393642</v>
       </c>
       <c r="B42" t="n">
-        <v>96045</v>
+        <v>101326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5424,45 +5220,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vretfallet, Upl</t>
+          <t>Marhällsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650528</v>
+        <v>650888</v>
       </c>
       <c r="R42" t="n">
-        <v>6671866</v>
+        <v>6672343</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5486,12 +5278,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5506,15 +5308,348 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122393643</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fulmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>650851</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6672282</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122393644</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fulmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>650753</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6672196</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122393653</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fulmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>650726</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6672208</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3733-2025 artfynd.xlsx
+++ b/artfynd/A 3733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393614</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393619</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393624</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126575818</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393670</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393610</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393583</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393585</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393587</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,6 +2313,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393589</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393598</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,6 +2561,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393599</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2600,6 +2685,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393669</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2716,6 +2806,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393577</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2835,6 +2930,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122390399</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2954,6 +3054,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3078,6 +3183,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393604</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3194,6 +3304,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393578</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3310,6 +3425,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393579</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3429,6 +3549,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393628</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3544,6 +3669,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393654</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3655,6 +3785,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393632</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3766,6 +3901,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393633</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3877,6 +4017,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393634</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3988,6 +4133,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393635</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4099,6 +4249,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393636</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4210,6 +4365,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393637</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4321,6 +4481,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393640</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4432,6 +4597,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393642</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4543,6 +4713,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393643</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4654,6 +4829,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393644</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4765,6 +4945,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393646</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4876,6 +5061,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393647</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4987,6 +5177,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393649</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5098,6 +5293,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393650</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5209,6 +5409,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393651</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5320,6 +5525,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393652</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5431,6 +5641,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393653</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5540,6 +5755,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126575816</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5650,8 +5870,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393622</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>